--- a/Code/Pricing/swaption_vol_comparison.xlsx
+++ b/Code/Pricing/swaption_vol_comparison.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X101"/>
+  <dimension ref="A1:P101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,55 +503,15 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>forward_swap_bp</t>
+          <t>vol_error</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>annuity</t>
+          <t>vol_error_bp</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>strike_bp</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>mean_payoff_Te</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>mean_df_to_exp</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>mc_std</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>mc_stderr</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>n_valid_paths</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>vol_error</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>vol_error_bp</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>abs_vol_error_bp</t>
         </is>
@@ -591,46 +551,22 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007274981091949192</v>
+        <v>0.07247639221296398</v>
       </c>
       <c r="L2" t="n">
-        <v>72.74981091949192</v>
+        <v>724.7639221296398</v>
       </c>
       <c r="M2" t="n">
-        <v>0.002817626152603683</v>
+        <v>0.02801706087463868</v>
       </c>
       <c r="N2" t="n">
-        <v>153.7290169976138</v>
+        <v>0.06807639221296398</v>
       </c>
       <c r="O2" t="n">
-        <v>0.970826080808937</v>
+        <v>680.7639221296398</v>
       </c>
       <c r="P2" t="n">
-        <v>153.7290169976138</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.00288990714178074</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.9783255835131122</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.004016190969655986</v>
-      </c>
-      <c r="T2" t="n">
-        <v>8.980476018771579e-05</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0.002874981091949192</v>
-      </c>
-      <c r="W2" t="n">
-        <v>28.74981091949192</v>
-      </c>
-      <c r="X2" t="n">
-        <v>28.74981091949192</v>
+        <v>680.7639221296398</v>
       </c>
     </row>
     <row r="3">
@@ -667,46 +603,22 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0006416572185139406</v>
+        <v>0.0297795209728408</v>
       </c>
       <c r="L3" t="n">
-        <v>6.416572185139406</v>
+        <v>297.7952097284081</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001184408650720786</v>
+        <v>0.05481691944333134</v>
       </c>
       <c r="N3" t="n">
-        <v>237.1979145302094</v>
+        <v>0.0265095209728408</v>
       </c>
       <c r="O3" t="n">
-        <v>4.626881965872833</v>
+        <v>265.0952097284081</v>
       </c>
       <c r="P3" t="n">
-        <v>237.1979145302094</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.001214176649116885</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.9783255835131122</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.008019263773414411</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0.0001793161892685609</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2000</v>
-      </c>
-      <c r="V3" t="n">
-        <v>-0.00262834278148606</v>
-      </c>
-      <c r="W3" t="n">
-        <v>-26.2834278148606</v>
-      </c>
-      <c r="X3" t="n">
-        <v>26.2834278148606</v>
+        <v>265.0952097284081</v>
       </c>
     </row>
     <row r="4">
@@ -743,46 +655,22 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>7.329333733479077e-05</v>
+        <v>0.009878443436279867</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7329333733479078</v>
+        <v>98.78443436279868</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0002507700370436377</v>
+        <v>0.03369212244672555</v>
       </c>
       <c r="N4" t="n">
-        <v>296.6613339611344</v>
+        <v>0.007038443436279867</v>
       </c>
       <c r="O4" t="n">
-        <v>8.576322052474865</v>
+        <v>70.38443436279869</v>
       </c>
       <c r="P4" t="n">
-        <v>296.6613339611344</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.0002580563493805513</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.9783255835131122</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.0028237362467882</v>
-      </c>
-      <c r="T4" t="n">
-        <v>6.314066198348536e-05</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2000</v>
-      </c>
-      <c r="V4" t="n">
-        <v>-0.002766706662665209</v>
-      </c>
-      <c r="W4" t="n">
-        <v>-27.66706662665209</v>
-      </c>
-      <c r="X4" t="n">
-        <v>27.66706662665209</v>
+        <v>70.38443436279869</v>
       </c>
     </row>
     <row r="5">
@@ -819,46 +707,22 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0006597764649677024</v>
+        <v>0.02867418838579638</v>
       </c>
       <c r="L5" t="n">
-        <v>6.597764649677024</v>
+        <v>286.7418838579638</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0005155809896933859</v>
+        <v>0.02230624821909483</v>
       </c>
       <c r="N5" t="n">
-        <v>300.2055364446912</v>
+        <v>0.02598418838579639</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8760018194085302</v>
+        <v>259.8418838579639</v>
       </c>
       <c r="P5" t="n">
-        <v>300.2055364446912</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.0005094114987107507</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.9428125483195795</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.005632059637711017</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.0001259996976392084</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1998</v>
-      </c>
-      <c r="V5" t="n">
-        <v>-0.002030223535032297</v>
-      </c>
-      <c r="W5" t="n">
-        <v>-20.30223535032297</v>
-      </c>
-      <c r="X5" t="n">
-        <v>20.30223535032297</v>
+        <v>259.8418838579639</v>
       </c>
     </row>
     <row r="6">
@@ -895,46 +759,22 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001484742089900685</v>
+        <v>0.01001367830992287</v>
       </c>
       <c r="L6" t="n">
-        <v>14.84742089900685</v>
+        <v>100.1367830992287</v>
       </c>
       <c r="M6" t="n">
-        <v>0.005422585578771787</v>
+        <v>0.03641424339527974</v>
       </c>
       <c r="N6" t="n">
-        <v>346.6872617350284</v>
+        <v>0.007743678309922874</v>
       </c>
       <c r="O6" t="n">
-        <v>4.094117725350532</v>
+        <v>77.43678309922873</v>
       </c>
       <c r="P6" t="n">
-        <v>346.6872617350284</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.005612593531170485</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.9404610795026426</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.05593197224703408</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0.001296891552376398</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1860</v>
-      </c>
-      <c r="V6" t="n">
-        <v>-0.0007852579100993148</v>
-      </c>
-      <c r="W6" t="n">
-        <v>-7.852579100993148</v>
-      </c>
-      <c r="X6" t="n">
-        <v>7.852579100993148</v>
+        <v>77.43678309922873</v>
       </c>
     </row>
     <row r="7">
@@ -971,46 +811,22 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0002381527020050234</v>
+        <v>0.00362767397022906</v>
       </c>
       <c r="L7" t="n">
-        <v>2.381527020050234</v>
+        <v>36.27673970229061</v>
       </c>
       <c r="M7" t="n">
-        <v>0.001590154645078526</v>
+        <v>0.02418603228250612</v>
       </c>
       <c r="N7" t="n">
-        <v>366.5114049596177</v>
+        <v>0.00146767397022906</v>
       </c>
       <c r="O7" t="n">
-        <v>7.48494788708423</v>
+        <v>14.6767397022906</v>
       </c>
       <c r="P7" t="n">
-        <v>366.5114049596177</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.001632685178653288</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.9404610795026426</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.02028451121240415</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.0004703358415337527</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1860</v>
-      </c>
-      <c r="V7" t="n">
-        <v>-0.001921847297994977</v>
-      </c>
-      <c r="W7" t="n">
-        <v>-19.21847297994977</v>
-      </c>
-      <c r="X7" t="n">
-        <v>19.21847297994977</v>
+        <v>14.6767397022906</v>
       </c>
     </row>
     <row r="8">
@@ -1047,46 +863,22 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002186811106913</v>
+        <v>0.02093742971386763</v>
       </c>
       <c r="L8" t="n">
-        <v>21.86811106913</v>
+        <v>209.3742971386763</v>
       </c>
       <c r="M8" t="n">
-        <v>0.002017582350551031</v>
+        <v>0.0193027880944054</v>
       </c>
       <c r="N8" t="n">
-        <v>397.0585519576147</v>
+        <v>0.01907742971386763</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7313241806600286</v>
+        <v>190.7742971386763</v>
       </c>
       <c r="P8" t="n">
-        <v>397.0585519576147</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.001926713442229632</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.9565707363181595</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.01386666663340906</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0.0003104564054908932</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1995</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0.0003268111069129999</v>
-      </c>
-      <c r="W8" t="n">
-        <v>3.268111069130001</v>
-      </c>
-      <c r="X8" t="n">
-        <v>3.268111069130001</v>
+        <v>190.7742971386763</v>
       </c>
     </row>
     <row r="9">
@@ -1123,46 +915,22 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001856098353680047</v>
+        <v>0.008309646653175339</v>
       </c>
       <c r="L9" t="n">
-        <v>18.56098353680047</v>
+        <v>83.09646653175339</v>
       </c>
       <c r="M9" t="n">
-        <v>0.007939937593097836</v>
+        <v>0.03561492217925348</v>
       </c>
       <c r="N9" t="n">
-        <v>390.4472473033644</v>
+        <v>0.006479646653175339</v>
       </c>
       <c r="O9" t="n">
-        <v>3.390830161733698</v>
+        <v>64.7964665317534</v>
       </c>
       <c r="P9" t="n">
-        <v>390.4472473033644</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.008121090851556408</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.9516812263562568</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.06078282844513474</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0.001470743617335684</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1708</v>
-      </c>
-      <c r="V9" t="n">
-        <v>2.609835368004663e-05</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0.2609835368004667</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0.2609835368004667</v>
+        <v>64.7964665317534</v>
       </c>
     </row>
     <row r="10">
@@ -1199,46 +967,22 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0003315729758779378</v>
+        <v>0.002755734748941127</v>
       </c>
       <c r="L10" t="n">
-        <v>3.315729758779379</v>
+        <v>27.55734748941127</v>
       </c>
       <c r="M10" t="n">
-        <v>0.002604193439009877</v>
+        <v>0.02169124358179503</v>
       </c>
       <c r="N10" t="n">
-        <v>369.5426389599409</v>
+        <v>0.0007957347489411272</v>
       </c>
       <c r="O10" t="n">
-        <v>6.225640625714862</v>
+        <v>7.957347489411269</v>
       </c>
       <c r="P10" t="n">
-        <v>369.5426389599409</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0.002627328240799008</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.9516812263562568</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.02564937008606356</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0.0006206300086349198</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1708</v>
-      </c>
-      <c r="V10" t="n">
-        <v>-0.001628427024122062</v>
-      </c>
-      <c r="W10" t="n">
-        <v>-16.28427024122062</v>
-      </c>
-      <c r="X10" t="n">
-        <v>16.28427024122062</v>
+        <v>7.957347489411269</v>
       </c>
     </row>
     <row r="11">
@@ -1275,46 +1019,22 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.00761101748290131</v>
+        <v>0.07429280276078881</v>
       </c>
       <c r="L11" t="n">
-        <v>76.11017482901309</v>
+        <v>742.9280276078881</v>
       </c>
       <c r="M11" t="n">
-        <v>0.002946096835782938</v>
+        <v>0.02873236502175141</v>
       </c>
       <c r="N11" t="n">
-        <v>159.1237844860107</v>
+        <v>0.06907280276078881</v>
       </c>
       <c r="O11" t="n">
-        <v>0.9702736388353915</v>
+        <v>690.7280276078881</v>
       </c>
       <c r="P11" t="n">
-        <v>159.1237844860107</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0.003024221090187314</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.9773801323949484</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0.004064952799236297</v>
-      </c>
-      <c r="T11" t="n">
-        <v>9.089510784420415e-05</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2000</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0.002391017482901309</v>
-      </c>
-      <c r="W11" t="n">
-        <v>23.91017482901309</v>
-      </c>
-      <c r="X11" t="n">
-        <v>23.91017482901309</v>
+        <v>690.7280276078881</v>
       </c>
     </row>
     <row r="12">
@@ -1351,46 +1071,22 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0004757608215874391</v>
+        <v>0.02904816914415234</v>
       </c>
       <c r="L12" t="n">
-        <v>4.757608215874391</v>
+        <v>290.4816914415234</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0008745870449395158</v>
+        <v>0.05326991117295664</v>
       </c>
       <c r="N12" t="n">
-        <v>254.2639072563602</v>
+        <v>0.02573816914415234</v>
       </c>
       <c r="O12" t="n">
-        <v>4.60791329592164</v>
+        <v>257.3816914415234</v>
       </c>
       <c r="P12" t="n">
-        <v>254.2639072563602</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0.0008966986004557699</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.9773801323949484</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0.007884314327281618</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0.0001762986279177722</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2000</v>
-      </c>
-      <c r="V12" t="n">
-        <v>-0.002834239178412561</v>
-      </c>
-      <c r="W12" t="n">
-        <v>-28.34239178412561</v>
-      </c>
-      <c r="X12" t="n">
-        <v>28.34239178412561</v>
+        <v>257.3816914415234</v>
       </c>
     </row>
     <row r="13">
@@ -1427,46 +1123,22 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>3.404539805917595e-05</v>
+        <v>0.008566682250483595</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3404539805917595</v>
+        <v>85.66682250483595</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0001152757502549823</v>
+        <v>0.02889160520792216</v>
       </c>
       <c r="N13" t="n">
-        <v>321.5205379800133</v>
+        <v>0.005716682250483595</v>
       </c>
       <c r="O13" t="n">
-        <v>8.48729847323848</v>
+        <v>57.16682250483595</v>
       </c>
       <c r="P13" t="n">
-        <v>321.5205379800133</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0.0001186867235520886</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0.9773801323949484</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0.001722705947977535</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3.852087604920985e-05</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2000</v>
-      </c>
-      <c r="V13" t="n">
-        <v>-0.002815954601940824</v>
-      </c>
-      <c r="W13" t="n">
-        <v>-28.15954601940824</v>
-      </c>
-      <c r="X13" t="n">
-        <v>28.15954601940824</v>
+        <v>57.16682250483595</v>
       </c>
     </row>
     <row r="14">
@@ -1503,46 +1175,22 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0005831667248634802</v>
+        <v>0.02809750847034492</v>
       </c>
       <c r="L14" t="n">
-        <v>5.831667248634802</v>
+        <v>280.9750847034492</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0004518380764786566</v>
+        <v>0.02165020887049022</v>
       </c>
       <c r="N14" t="n">
-        <v>325.3394180437612</v>
+        <v>0.02549750847034492</v>
       </c>
       <c r="O14" t="n">
-        <v>0.8685503962832847</v>
+        <v>254.9750847034492</v>
       </c>
       <c r="P14" t="n">
-        <v>325.3394180437612</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0.0004468979650920826</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0.9396413217525528</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.005331531101887936</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0.0001192763127531329</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1998</v>
-      </c>
-      <c r="V14" t="n">
-        <v>-0.002016833275136519</v>
-      </c>
-      <c r="W14" t="n">
-        <v>-20.1683327513652</v>
-      </c>
-      <c r="X14" t="n">
-        <v>20.1683327513652</v>
+        <v>254.9750847034492</v>
       </c>
     </row>
     <row r="15">
@@ -1579,46 +1227,22 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.001259167008936579</v>
+        <v>0.009521659195879155</v>
       </c>
       <c r="L15" t="n">
-        <v>12.59167008936579</v>
+        <v>95.21659195879155</v>
       </c>
       <c r="M15" t="n">
-        <v>0.004532454178546365</v>
+        <v>0.03406074576108364</v>
       </c>
       <c r="N15" t="n">
-        <v>378.5307136208181</v>
+        <v>0.007311659195879155</v>
       </c>
       <c r="O15" t="n">
-        <v>4.035106650536142</v>
+        <v>73.11659195879156</v>
       </c>
       <c r="P15" t="n">
-        <v>378.5307136208181</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0.00469395647018663</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0.9373307139867234</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0.05204193889357207</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0.001206693563786163</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1860</v>
-      </c>
-      <c r="V15" t="n">
-        <v>-0.0009508329910634212</v>
-      </c>
-      <c r="W15" t="n">
-        <v>-9.508329910634211</v>
-      </c>
-      <c r="X15" t="n">
-        <v>9.508329910634211</v>
+        <v>73.11659195879156</v>
       </c>
     </row>
     <row r="16">
@@ -1655,46 +1279,22 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0001591682639028975</v>
+        <v>0.003030904820210473</v>
       </c>
       <c r="L16" t="n">
-        <v>1.591682639028975</v>
+        <v>30.30904820210473</v>
       </c>
       <c r="M16" t="n">
-        <v>0.00103864422919939</v>
+        <v>0.01971096298201401</v>
       </c>
       <c r="N16" t="n">
-        <v>402.325008471737</v>
+        <v>0.000890904820210473</v>
       </c>
       <c r="O16" t="n">
-        <v>7.315015743561179</v>
+        <v>8.909048202104731</v>
       </c>
       <c r="P16" t="n">
-        <v>402.325008471737</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0.001062881542541092</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.9373307139867234</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0.0162678906549329</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0.0003772026824332871</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1860</v>
-      </c>
-      <c r="V16" t="n">
-        <v>-0.001980831736097102</v>
-      </c>
-      <c r="W16" t="n">
-        <v>-19.80831736097102</v>
-      </c>
-      <c r="X16" t="n">
-        <v>19.80831736097102</v>
+        <v>8.909048202104731</v>
       </c>
     </row>
     <row r="17">
@@ -1731,46 +1331,22 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.002040856778284215</v>
+        <v>0.01923338765254277</v>
       </c>
       <c r="L17" t="n">
-        <v>20.40856778284214</v>
+        <v>192.3338765254277</v>
       </c>
       <c r="M17" t="n">
-        <v>0.001835303559550718</v>
+        <v>0.01724505374770265</v>
       </c>
       <c r="N17" t="n">
-        <v>438.2210129118191</v>
+        <v>0.01728338765254277</v>
       </c>
       <c r="O17" t="n">
-        <v>0.7128289230639834</v>
+        <v>172.8338765254277</v>
       </c>
       <c r="P17" t="n">
-        <v>438.2210129118191</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0.001757293343219749</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0.9522250982799846</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0.01316351533132525</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0.0002946399384429557</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1996</v>
-      </c>
-      <c r="V17" t="n">
-        <v>9.085677828421469e-05</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0.9085677828421446</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0.9085677828421446</v>
+        <v>172.8338765254277</v>
       </c>
     </row>
     <row r="18">
@@ -1807,46 +1383,22 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.001856844233628503</v>
+        <v>0.008333923867200492</v>
       </c>
       <c r="L18" t="n">
-        <v>18.56844233628503</v>
+        <v>83.33923867200492</v>
       </c>
       <c r="M18" t="n">
-        <v>0.007683292129176382</v>
+        <v>0.03448733796150007</v>
       </c>
       <c r="N18" t="n">
-        <v>431.5979287492955</v>
+        <v>0.006443923867200493</v>
       </c>
       <c r="O18" t="n">
-        <v>3.279909093025037</v>
+        <v>64.43923867200493</v>
       </c>
       <c r="P18" t="n">
-        <v>431.5979287492955</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0.007923067067343453</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0.9473364398773967</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0.05963217400146986</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0.001438277558861418</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1719</v>
-      </c>
-      <c r="V18" t="n">
-        <v>-3.315576637149685e-05</v>
-      </c>
-      <c r="W18" t="n">
-        <v>-0.3315576637149711</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0.3315576637149711</v>
+        <v>64.43923867200493</v>
       </c>
     </row>
     <row r="19">
@@ -1883,46 +1435,22 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0002564826005016048</v>
+        <v>0.0022644080585662</v>
       </c>
       <c r="L19" t="n">
-        <v>2.564826005016048</v>
+        <v>22.644080585662</v>
       </c>
       <c r="M19" t="n">
-        <v>0.001932326959229926</v>
+        <v>0.01706493379625957</v>
       </c>
       <c r="N19" t="n">
-        <v>408.4864019343058</v>
+        <v>0.0002444080585662003</v>
       </c>
       <c r="O19" t="n">
-        <v>5.971901540641207</v>
+        <v>2.444080585662004</v>
       </c>
       <c r="P19" t="n">
-        <v>408.4864019343058</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0.001966336322590885</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0.9472751915880768</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0.02146454566870349</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0.0005181590151815398</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1716</v>
-      </c>
-      <c r="V19" t="n">
-        <v>-0.001763517399498395</v>
-      </c>
-      <c r="W19" t="n">
-        <v>-17.63517399498395</v>
-      </c>
-      <c r="X19" t="n">
-        <v>17.63517399498395</v>
+        <v>2.444080585662004</v>
       </c>
     </row>
     <row r="20">
@@ -1959,46 +1487,22 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0.007782840160379687</v>
+        <v>0.07539133036132947</v>
       </c>
       <c r="L20" t="n">
-        <v>77.82840160379688</v>
+        <v>753.9133036132947</v>
       </c>
       <c r="M20" t="n">
-        <v>0.003008433310890248</v>
+        <v>0.02915329509838671</v>
       </c>
       <c r="N20" t="n">
-        <v>168.1967974199472</v>
+        <v>0.07052133036132947</v>
       </c>
       <c r="O20" t="n">
-        <v>0.9689295737831728</v>
+        <v>705.2133036132947</v>
       </c>
       <c r="P20" t="n">
-        <v>168.1967974199472</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0.003091742445393564</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0.9761505191692316</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0.004064007610251536</v>
-      </c>
-      <c r="T20" t="n">
-        <v>9.087397277598907e-05</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2000</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0.002912840160379687</v>
-      </c>
-      <c r="W20" t="n">
-        <v>29.12840160379687</v>
-      </c>
-      <c r="X20" t="n">
-        <v>29.12840160379687</v>
+        <v>705.2133036132947</v>
       </c>
     </row>
     <row r="21">
@@ -2035,46 +1539,22 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0003162844897220324</v>
+        <v>0.02685644726934613</v>
       </c>
       <c r="L21" t="n">
-        <v>3.162844897220324</v>
+        <v>268.5644726934614</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0005781875258878279</v>
+        <v>0.04902392635493893</v>
       </c>
       <c r="N21" t="n">
-        <v>274.5532273764169</v>
+        <v>0.02388644726934613</v>
       </c>
       <c r="O21" t="n">
-        <v>4.582270859070882</v>
+        <v>238.8644726934614</v>
       </c>
       <c r="P21" t="n">
-        <v>274.5532273764169</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0.0005931501013678834</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0.9761505191692316</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0.007071881382410986</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0.0001581320749988615</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2000</v>
-      </c>
-      <c r="V21" t="n">
-        <v>-0.002653715510277968</v>
-      </c>
-      <c r="W21" t="n">
-        <v>-26.53715510277967</v>
-      </c>
-      <c r="X21" t="n">
-        <v>26.53715510277967</v>
+        <v>238.8644726934614</v>
       </c>
     </row>
     <row r="22">
@@ -2111,46 +1591,22 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>1.358445202667346e-05</v>
+        <v>0.007615632029501113</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1358445202667346</v>
+        <v>76.15632029501113</v>
       </c>
       <c r="M22" t="n">
-        <v>4.544840727183373e-05</v>
+        <v>0.02537909598538159</v>
       </c>
       <c r="N22" t="n">
-        <v>347.3686130235387</v>
+        <v>0.005105632029501113</v>
       </c>
       <c r="O22" t="n">
-        <v>8.386224374809816</v>
+        <v>51.05632029501113</v>
       </c>
       <c r="P22" t="n">
-        <v>347.3686130235387</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>4.681419524719987e-05</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0.9761505191692316</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0.0009945243058777128</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.223823953218359e-05</v>
-      </c>
-      <c r="U22" t="n">
-        <v>2000</v>
-      </c>
-      <c r="V22" t="n">
-        <v>-0.002496415547973327</v>
-      </c>
-      <c r="W22" t="n">
-        <v>-24.96415547973327</v>
-      </c>
-      <c r="X22" t="n">
-        <v>24.96415547973327</v>
+        <v>51.05632029501113</v>
       </c>
     </row>
     <row r="23">
@@ -2187,46 +1643,22 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0005748379626893092</v>
+        <v>0.02625151121129364</v>
       </c>
       <c r="L23" t="n">
-        <v>5.748379626893091</v>
+        <v>262.5151121129364</v>
       </c>
       <c r="M23" t="n">
-        <v>0.000440702411309524</v>
+        <v>0.02001440993153041</v>
       </c>
       <c r="N23" t="n">
-        <v>352.2161320342585</v>
+        <v>0.02394151121129364</v>
       </c>
       <c r="O23" t="n">
-        <v>0.8594189335996715</v>
+        <v>239.4151121129364</v>
       </c>
       <c r="P23" t="n">
-        <v>352.2161320342585</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0.0004391278205281768</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0.935504199430235</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0.005496231493168527</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0.0001229302087827254</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1999</v>
-      </c>
-      <c r="V23" t="n">
-        <v>-0.001735162037310691</v>
-      </c>
-      <c r="W23" t="n">
-        <v>-17.35162037310691</v>
-      </c>
-      <c r="X23" t="n">
-        <v>17.35162037310691</v>
+        <v>239.4151121129364</v>
       </c>
     </row>
     <row r="24">
@@ -2263,46 +1695,22 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0008250688845080157</v>
+        <v>0.009164664946899305</v>
       </c>
       <c r="L24" t="n">
-        <v>8.250688845080157</v>
+        <v>91.64664946899305</v>
       </c>
       <c r="M24" t="n">
-        <v>0.002921570483287397</v>
+        <v>0.03222229247823918</v>
       </c>
       <c r="N24" t="n">
-        <v>409.921815420766</v>
+        <v>0.007234664946899305</v>
       </c>
       <c r="O24" t="n">
-        <v>3.969456903390038</v>
+        <v>72.34664946899305</v>
       </c>
       <c r="P24" t="n">
-        <v>409.921815420766</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0.003055613293657535</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0.933307906371917</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0.03845644730003209</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0.0008893001330855406</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1870</v>
-      </c>
-      <c r="V24" t="n">
-        <v>-0.001104931115491984</v>
-      </c>
-      <c r="W24" t="n">
-        <v>-11.04931115491984</v>
-      </c>
-      <c r="X24" t="n">
-        <v>11.04931115491984</v>
+        <v>72.34664946899305</v>
       </c>
     </row>
     <row r="25">
@@ -2339,46 +1747,22 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>7.810950009894677e-05</v>
+        <v>0.002483538947990661</v>
       </c>
       <c r="L25" t="n">
-        <v>0.7810950009894677</v>
+        <v>24.83538947990661</v>
       </c>
       <c r="M25" t="n">
-        <v>0.000497524919299279</v>
+        <v>0.01575059459977373</v>
       </c>
       <c r="N25" t="n">
-        <v>436.2689884474747</v>
+        <v>0.0006435389479906609</v>
       </c>
       <c r="O25" t="n">
-        <v>7.140290999376524</v>
+        <v>6.435389479906608</v>
       </c>
       <c r="P25" t="n">
-        <v>436.2689884474747</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0.0005157710166987433</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0.9332197331978811</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0.00994032627646666</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0.0002299917213883593</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1868</v>
-      </c>
-      <c r="V25" t="n">
-        <v>-0.001761890499901053</v>
-      </c>
-      <c r="W25" t="n">
-        <v>-17.61890499901053</v>
-      </c>
-      <c r="X25" t="n">
-        <v>17.61890499901053</v>
+        <v>6.435389479906608</v>
       </c>
     </row>
     <row r="26">
@@ -2415,46 +1799,22 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0.001908787576836813</v>
+        <v>0.01980217730034173</v>
       </c>
       <c r="L26" t="n">
-        <v>19.08787576836813</v>
+        <v>198.0217730034173</v>
       </c>
       <c r="M26" t="n">
-        <v>0.001670991661829978</v>
+        <v>0.01726331243617224</v>
       </c>
       <c r="N26" t="n">
-        <v>476.3808952810373</v>
+        <v>0.01810217730034173</v>
       </c>
       <c r="O26" t="n">
-        <v>0.6939155459485654</v>
+        <v>181.0217730034173</v>
       </c>
       <c r="P26" t="n">
-        <v>476.3808952810373</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0.001607117973033537</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0.9464058730433405</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0.01248352208783395</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0.0002794195993191717</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1996</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0.0002087875768368133</v>
-      </c>
-      <c r="W26" t="n">
-        <v>2.087875768368132</v>
-      </c>
-      <c r="X26" t="n">
-        <v>2.087875768368132</v>
+        <v>181.0217730034173</v>
       </c>
     </row>
     <row r="27">
@@ -2491,46 +1851,22 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0.001793831949419651</v>
+        <v>0.007535376682878945</v>
       </c>
       <c r="L27" t="n">
-        <v>17.93831949419651</v>
+        <v>75.35376682878945</v>
       </c>
       <c r="M27" t="n">
-        <v>0.007175717623832699</v>
+        <v>0.03011637984866795</v>
       </c>
       <c r="N27" t="n">
-        <v>469.2520978406968</v>
+        <v>0.005905376682878945</v>
       </c>
       <c r="O27" t="n">
-        <v>3.170834095986486</v>
+        <v>59.05376682878945</v>
       </c>
       <c r="P27" t="n">
-        <v>469.2520978406968</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0.007484878557207182</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0.9414340591121488</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0.05685478519860334</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0.001372487447978941</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1716</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0.0001638319494196509</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.638319494196509</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.638319494196509</v>
+        <v>59.05376682878945</v>
       </c>
     </row>
     <row r="28">
@@ -2567,46 +1903,22 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>0.0002119758409201301</v>
+        <v>0.001847829028847196</v>
       </c>
       <c r="L28" t="n">
-        <v>2.119758409201301</v>
+        <v>18.47829028847196</v>
       </c>
       <c r="M28" t="n">
-        <v>0.001532413470051482</v>
+        <v>0.01334355283229707</v>
       </c>
       <c r="N28" t="n">
-        <v>443.9965032872146</v>
+        <v>0.0001478290288471965</v>
       </c>
       <c r="O28" t="n">
-        <v>5.730328617365969</v>
+        <v>1.478290288471964</v>
       </c>
       <c r="P28" t="n">
-        <v>443.9965032872146</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0.001574690704244721</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0.9414271653317469</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0.01828131163781712</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0.0004414436660776881</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1715</v>
-      </c>
-      <c r="V28" t="n">
-        <v>-0.00148802415907987</v>
-      </c>
-      <c r="W28" t="n">
-        <v>-14.8802415907987</v>
-      </c>
-      <c r="X28" t="n">
-        <v>14.8802415907987</v>
+        <v>1.478290288471964</v>
       </c>
     </row>
     <row r="29">
@@ -2643,46 +1955,22 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>0.006885619744866052</v>
+        <v>0.07019240796894351</v>
       </c>
       <c r="L29" t="n">
-        <v>68.85619744866051</v>
+        <v>701.9240796894351</v>
       </c>
       <c r="M29" t="n">
-        <v>0.002642474495854341</v>
+        <v>0.02693207604672336</v>
       </c>
       <c r="N29" t="n">
-        <v>201.4873533368971</v>
+        <v>0.0660124079689435</v>
       </c>
       <c r="O29" t="n">
-        <v>0.9619615273176316</v>
+        <v>660.1240796894351</v>
       </c>
       <c r="P29" t="n">
-        <v>201.4873533368971</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0.002724141251779863</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0.973016403830862</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0.003753531157916887</v>
-      </c>
-      <c r="T29" t="n">
-        <v>8.393150824765656e-05</v>
-      </c>
-      <c r="U29" t="n">
-        <v>2000</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0.002705619744866052</v>
-      </c>
-      <c r="W29" t="n">
-        <v>27.05619744866051</v>
-      </c>
-      <c r="X29" t="n">
-        <v>27.05619744866051</v>
+        <v>660.1240796894351</v>
       </c>
     </row>
     <row r="30">
@@ -2719,46 +2007,22 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0.0001561384801946678</v>
+        <v>0.02482230304410903</v>
       </c>
       <c r="L30" t="n">
-        <v>1.561384801946678</v>
+        <v>248.2230304410903</v>
       </c>
       <c r="M30" t="n">
-        <v>0.0002815300385395283</v>
+        <v>0.04473805010364212</v>
       </c>
       <c r="N30" t="n">
-        <v>306.9880197909498</v>
+        <v>0.02201230304410903</v>
       </c>
       <c r="O30" t="n">
-        <v>4.519649185013884</v>
+        <v>220.1230304410903</v>
       </c>
       <c r="P30" t="n">
-        <v>306.9880197909498</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0.0002899564853771679</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0.973016403830862</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0.004126247624983094</v>
-      </c>
-      <c r="T30" t="n">
-        <v>9.226570181459258e-05</v>
-      </c>
-      <c r="U30" t="n">
-        <v>2000</v>
-      </c>
-      <c r="V30" t="n">
-        <v>-0.002653861519805332</v>
-      </c>
-      <c r="W30" t="n">
-        <v>-26.53861519805332</v>
-      </c>
-      <c r="X30" t="n">
-        <v>26.53861519805332</v>
+        <v>220.1230304410903</v>
       </c>
     </row>
     <row r="31">
@@ -2795,46 +2059,22 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>1.936420401235536e-05</v>
+        <v>0.00720243589662915</v>
       </c>
       <c r="L31" t="n">
-        <v>0.1936420401235535</v>
+        <v>72.0243589662915</v>
       </c>
       <c r="M31" t="n">
-        <v>6.363620554802448e-05</v>
+        <v>0.02363337202053932</v>
       </c>
       <c r="N31" t="n">
-        <v>368.6115540355761</v>
+        <v>0.00490243589662915</v>
       </c>
       <c r="O31" t="n">
-        <v>8.237483555488842</v>
+        <v>49.0243589662915</v>
       </c>
       <c r="P31" t="n">
-        <v>368.6115540355761</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>6.575840508487369e-05</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0.973016403830862</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0.001201796101113722</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.687297777184492e-05</v>
-      </c>
-      <c r="U31" t="n">
-        <v>2000</v>
-      </c>
-      <c r="V31" t="n">
-        <v>-0.002280635795987645</v>
-      </c>
-      <c r="W31" t="n">
-        <v>-22.80635795987645</v>
-      </c>
-      <c r="X31" t="n">
-        <v>22.80635795987645</v>
+        <v>49.0243589662915</v>
       </c>
     </row>
     <row r="32">
@@ -2871,46 +2111,22 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.0008980397189346796</v>
+        <v>0.02398434390837063</v>
       </c>
       <c r="L32" t="n">
-        <v>8.980397189346796</v>
+        <v>239.8434390837063</v>
       </c>
       <c r="M32" t="n">
-        <v>0.0006750097046811469</v>
+        <v>0.01798372412079137</v>
       </c>
       <c r="N32" t="n">
-        <v>376.3812072687184</v>
+        <v>0.02145434390837063</v>
       </c>
       <c r="O32" t="n">
-        <v>0.8425960201870273</v>
+        <v>214.5434390837063</v>
       </c>
       <c r="P32" t="n">
-        <v>376.3812072687184</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0.0006849214433123277</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0.9247316993780706</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0.01847457139724316</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0.0004135176996596169</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1996</v>
-      </c>
-      <c r="V32" t="n">
-        <v>-0.001631960281065321</v>
-      </c>
-      <c r="W32" t="n">
-        <v>-16.3196028106532</v>
-      </c>
-      <c r="X32" t="n">
-        <v>16.3196028106532</v>
+        <v>214.5434390837063</v>
       </c>
     </row>
     <row r="33">
@@ -2947,46 +2163,22 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.000549495977890466</v>
+        <v>0.009513132044752107</v>
       </c>
       <c r="L33" t="n">
-        <v>5.49495977890466</v>
+        <v>95.13132044752108</v>
       </c>
       <c r="M33" t="n">
-        <v>0.00190325397501686</v>
+        <v>0.0328453405964013</v>
       </c>
       <c r="N33" t="n">
-        <v>423.2092155169656</v>
+        <v>0.007443132044752107</v>
       </c>
       <c r="O33" t="n">
-        <v>3.882729716602364</v>
+        <v>74.43132044752107</v>
       </c>
       <c r="P33" t="n">
-        <v>423.2092155169656</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0.002014575897219421</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0.9231587491663151</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0.03285920126392197</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0.0007546365500213517</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1896</v>
-      </c>
-      <c r="V33" t="n">
-        <v>-0.001520504022109534</v>
-      </c>
-      <c r="W33" t="n">
-        <v>-15.20504022109534</v>
-      </c>
-      <c r="X33" t="n">
-        <v>15.20504022109534</v>
+        <v>74.43132044752107</v>
       </c>
     </row>
     <row r="34">
@@ -3023,46 +2215,22 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>4.405732900941845e-05</v>
+        <v>0.002521111737684397</v>
       </c>
       <c r="L34" t="n">
-        <v>0.4405732900941844</v>
+        <v>25.21111737684397</v>
       </c>
       <c r="M34" t="n">
-        <v>0.0002743909522019742</v>
+        <v>0.01568269808153866</v>
       </c>
       <c r="N34" t="n">
-        <v>442.1125348405965</v>
+        <v>0.0005811117376843967</v>
       </c>
       <c r="O34" t="n">
-        <v>6.981625584348741</v>
+        <v>5.811117376843967</v>
       </c>
       <c r="P34" t="n">
-        <v>442.1125348405965</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0.0002847001951460325</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0.9231403698231233</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0.008075504775818523</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0.0001855090370879603</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1895</v>
-      </c>
-      <c r="V34" t="n">
-        <v>-0.001895942670990582</v>
-      </c>
-      <c r="W34" t="n">
-        <v>-18.95942670990581</v>
-      </c>
-      <c r="X34" t="n">
-        <v>18.95942670990581</v>
+        <v>5.811117376843967</v>
       </c>
     </row>
     <row r="35">
@@ -3099,46 +2267,22 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>0.001860764229986449</v>
+        <v>0.01821482915321607</v>
       </c>
       <c r="L35" t="n">
-        <v>18.60764229986449</v>
+        <v>182.1482915321607</v>
       </c>
       <c r="M35" t="n">
-        <v>0.001590886997510353</v>
+        <v>0.01556544216516182</v>
       </c>
       <c r="N35" t="n">
-        <v>476.4400915082477</v>
+        <v>0.01639482915321607</v>
       </c>
       <c r="O35" t="n">
-        <v>0.677700674059622</v>
+        <v>163.9482915321607</v>
       </c>
       <c r="P35" t="n">
-        <v>476.4400915082477</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>0.001554545536727809</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0.9316224036618266</v>
-      </c>
-      <c r="S35" t="n">
-        <v>0.01208130099147815</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0.0002704166547342467</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1996</v>
-      </c>
-      <c r="V35" t="n">
-        <v>4.076422998644871e-05</v>
-      </c>
-      <c r="W35" t="n">
-        <v>0.407642299864488</v>
-      </c>
-      <c r="X35" t="n">
-        <v>0.407642299864488</v>
+        <v>163.9482915321607</v>
       </c>
     </row>
     <row r="36">
@@ -3175,46 +2319,22 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>0.001688041326991198</v>
+        <v>0.007848762009005892</v>
       </c>
       <c r="L36" t="n">
-        <v>16.88041326991198</v>
+        <v>78.48762009005893</v>
       </c>
       <c r="M36" t="n">
-        <v>0.006599334220968685</v>
+        <v>0.03072339582981062</v>
       </c>
       <c r="N36" t="n">
-        <v>465.7972544351474</v>
+        <v>0.006158762009005892</v>
       </c>
       <c r="O36" t="n">
-        <v>3.098895867746378</v>
+        <v>61.58762009005893</v>
       </c>
       <c r="P36" t="n">
-        <v>465.7972544351474</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>0.007079254023515848</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0.9266445559443656</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0.05672290767609616</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0.001368506628786699</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1718</v>
-      </c>
-      <c r="V36" t="n">
-        <v>-1.958673008801721e-06</v>
-      </c>
-      <c r="W36" t="n">
-        <v>-0.01958673008801526</v>
-      </c>
-      <c r="X36" t="n">
-        <v>0.01958673008801526</v>
+        <v>61.58762009005893</v>
       </c>
     </row>
     <row r="37">
@@ -3251,46 +2371,22 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>0.0002340618845318152</v>
+        <v>0.001842175870615113</v>
       </c>
       <c r="L37" t="n">
-        <v>2.340618845318152</v>
+        <v>18.42175870615113</v>
       </c>
       <c r="M37" t="n">
-        <v>0.001656051318689982</v>
+        <v>0.01301905504987667</v>
       </c>
       <c r="N37" t="n">
-        <v>438.4433592651276</v>
+        <v>0.0001121758706151127</v>
       </c>
       <c r="O37" t="n">
-        <v>5.608323124227677</v>
+        <v>1.121758706151127</v>
       </c>
       <c r="P37" t="n">
-        <v>438.4433592651276</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0.001784494547419457</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0.9266526756710868</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0.0190514876619116</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0.0004597732989095801</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1717</v>
-      </c>
-      <c r="V37" t="n">
-        <v>-0.001495938115468185</v>
-      </c>
-      <c r="W37" t="n">
-        <v>-14.95938115468185</v>
-      </c>
-      <c r="X37" t="n">
-        <v>14.95938115468185</v>
+        <v>1.121758706151127</v>
       </c>
     </row>
     <row r="38">
@@ -3327,46 +2423,22 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>0.006633767843922526</v>
+        <v>0.06864096166247205</v>
       </c>
       <c r="L38" t="n">
-        <v>66.33767843922526</v>
+        <v>686.4096166247205</v>
       </c>
       <c r="M38" t="n">
-        <v>0.002543475271064341</v>
+        <v>0.0263020683078279</v>
       </c>
       <c r="N38" t="n">
-        <v>205.4430474234921</v>
+        <v>0.06469096166247205</v>
       </c>
       <c r="O38" t="n">
-        <v>0.9610747889098248</v>
+        <v>646.9096166247205</v>
       </c>
       <c r="P38" t="n">
-        <v>205.4430474234921</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0.002622770949389926</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0.9727821663622355</v>
-      </c>
-      <c r="S38" t="n">
-        <v>0.003685509646542701</v>
-      </c>
-      <c r="T38" t="n">
-        <v>8.241050101400702e-05</v>
-      </c>
-      <c r="U38" t="n">
-        <v>2000</v>
-      </c>
-      <c r="V38" t="n">
-        <v>0.002683767843922526</v>
-      </c>
-      <c r="W38" t="n">
-        <v>26.83767843922526</v>
-      </c>
-      <c r="X38" t="n">
-        <v>26.83767843922526</v>
+        <v>646.9096166247205</v>
       </c>
     </row>
     <row r="39">
@@ -3403,46 +2475,22 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>0.0001584239756636635</v>
+        <v>0.02516789918369127</v>
       </c>
       <c r="L39" t="n">
-        <v>1.584239756636635</v>
+        <v>251.6789918369127</v>
       </c>
       <c r="M39" t="n">
-        <v>0.0002853931096028974</v>
+        <v>0.04531550841190976</v>
       </c>
       <c r="N39" t="n">
-        <v>307.2083048312878</v>
+        <v>0.02240789918369127</v>
       </c>
       <c r="O39" t="n">
-        <v>4.515569281219387</v>
+        <v>224.0789918369127</v>
       </c>
       <c r="P39" t="n">
-        <v>307.2083048312878</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0.0002941029212651763</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0.9727821663622355</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0.003980040406379633</v>
-      </c>
-      <c r="T39" t="n">
-        <v>8.899640901860746e-05</v>
-      </c>
-      <c r="U39" t="n">
-        <v>2000</v>
-      </c>
-      <c r="V39" t="n">
-        <v>-0.002601576024336337</v>
-      </c>
-      <c r="W39" t="n">
-        <v>-26.01576024336337</v>
-      </c>
-      <c r="X39" t="n">
-        <v>26.01576024336337</v>
+        <v>224.0789918369127</v>
       </c>
     </row>
     <row r="40">
@@ -3479,46 +2527,22 @@
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>2.525798473015726e-05</v>
+        <v>0.007508962213120434</v>
       </c>
       <c r="L40" t="n">
-        <v>0.2525798473015726</v>
+        <v>75.08962213120434</v>
       </c>
       <c r="M40" t="n">
-        <v>8.30014788811152e-05</v>
+        <v>0.02464458795836952</v>
       </c>
       <c r="N40" t="n">
-        <v>365.9226541505203</v>
+        <v>0.005168962213120434</v>
       </c>
       <c r="O40" t="n">
-        <v>8.237151776847076</v>
+        <v>51.68962213120434</v>
       </c>
       <c r="P40" t="n">
-        <v>365.9226541505203</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>8.580497494281742e-05</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0.9727821663622355</v>
-      </c>
-      <c r="S40" t="n">
-        <v>0.001412952112645908</v>
-      </c>
-      <c r="T40" t="n">
-        <v>3.159456972828191e-05</v>
-      </c>
-      <c r="U40" t="n">
-        <v>2000</v>
-      </c>
-      <c r="V40" t="n">
-        <v>-0.002314742015269843</v>
-      </c>
-      <c r="W40" t="n">
-        <v>-23.14742015269843</v>
-      </c>
-      <c r="X40" t="n">
-        <v>23.14742015269843</v>
+        <v>51.68962213120434</v>
       </c>
     </row>
     <row r="41">
@@ -3555,46 +2579,22 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>0.0009189123605350631</v>
+        <v>0.02491527132675368</v>
       </c>
       <c r="L41" t="n">
-        <v>9.18912360535063</v>
+        <v>249.1527132675368</v>
       </c>
       <c r="M41" t="n">
-        <v>0.0006902898207348748</v>
+        <v>0.01867793713935824</v>
       </c>
       <c r="N41" t="n">
-        <v>373.5186106740358</v>
+        <v>0.02250527132675368</v>
       </c>
       <c r="O41" t="n">
-        <v>0.8420973638302127</v>
+        <v>225.0527132675368</v>
       </c>
       <c r="P41" t="n">
-        <v>373.5186106740358</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>0.0007013987172161509</v>
-      </c>
-      <c r="R41" t="n">
-        <v>0.9239008836300896</v>
-      </c>
-      <c r="S41" t="n">
-        <v>0.01912369430941225</v>
-      </c>
-      <c r="T41" t="n">
-        <v>0.0004282616796055643</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1994</v>
-      </c>
-      <c r="V41" t="n">
-        <v>-0.001491087639464937</v>
-      </c>
-      <c r="W41" t="n">
-        <v>-14.91087639464937</v>
-      </c>
-      <c r="X41" t="n">
-        <v>14.91087639464937</v>
+        <v>225.0527132675368</v>
       </c>
     </row>
     <row r="42">
@@ -3631,46 +2631,22 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0.0005352447780252894</v>
+        <v>0.009019633474729213</v>
       </c>
       <c r="L42" t="n">
-        <v>5.352447780252894</v>
+        <v>90.19633474729213</v>
       </c>
       <c r="M42" t="n">
-        <v>0.001854631553781722</v>
+        <v>0.03117380716503465</v>
       </c>
       <c r="N42" t="n">
-        <v>417.9545740828327</v>
+        <v>0.006969633474729214</v>
       </c>
       <c r="O42" t="n">
-        <v>3.884276501286981</v>
+        <v>69.69633474729213</v>
       </c>
       <c r="P42" t="n">
-        <v>417.9545740828327</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>0.001966222161982421</v>
-      </c>
-      <c r="R42" t="n">
-        <v>0.9223742235259468</v>
-      </c>
-      <c r="S42" t="n">
-        <v>0.03251122188306082</v>
-      </c>
-      <c r="T42" t="n">
-        <v>0.0007464481166805551</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1897</v>
-      </c>
-      <c r="V42" t="n">
-        <v>-0.001514755221974711</v>
-      </c>
-      <c r="W42" t="n">
-        <v>-15.14755221974711</v>
-      </c>
-      <c r="X42" t="n">
-        <v>15.14755221974711</v>
+        <v>69.69633474729213</v>
       </c>
     </row>
     <row r="43">
@@ -3707,46 +2683,22 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>4.482781689307933e-05</v>
+        <v>0.002554874506100716</v>
       </c>
       <c r="L43" t="n">
-        <v>0.4482781689307933</v>
+        <v>25.54874506100716</v>
       </c>
       <c r="M43" t="n">
-        <v>0.0002797590542937093</v>
+        <v>0.0159340238139618</v>
       </c>
       <c r="N43" t="n">
-        <v>435.4255162477696</v>
+        <v>0.0005648745061007164</v>
       </c>
       <c r="O43" t="n">
-        <v>6.995866186230058</v>
+        <v>5.648745061007165</v>
       </c>
       <c r="P43" t="n">
-        <v>435.4255162477696</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>0.0002907086306416121</v>
-      </c>
-      <c r="R43" t="n">
-        <v>0.9223529026944223</v>
-      </c>
-      <c r="S43" t="n">
-        <v>0.00867019854158251</v>
-      </c>
-      <c r="T43" t="n">
-        <v>0.0001991177041361549</v>
-      </c>
-      <c r="U43" t="n">
-        <v>1896</v>
-      </c>
-      <c r="V43" t="n">
-        <v>-0.001945172183106921</v>
-      </c>
-      <c r="W43" t="n">
-        <v>-19.4517218310692</v>
-      </c>
-      <c r="X43" t="n">
-        <v>19.4517218310692</v>
+        <v>5.648745061007165</v>
       </c>
     </row>
     <row r="44">
@@ -3783,46 +2735,22 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>0.001878750239778398</v>
+        <v>0.01821081871375253</v>
       </c>
       <c r="L44" t="n">
-        <v>18.78750239778398</v>
+        <v>182.1081871375252</v>
       </c>
       <c r="M44" t="n">
-        <v>0.001610300041130688</v>
+        <v>0.01561117466715312</v>
       </c>
       <c r="N44" t="n">
-        <v>468.0988980152745</v>
+        <v>0.01645081871375252</v>
       </c>
       <c r="O44" t="n">
-        <v>0.6794033581709216</v>
+        <v>164.5081871375253</v>
       </c>
       <c r="P44" t="n">
-        <v>468.0988980152745</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>0.001575883997650249</v>
-      </c>
-      <c r="R44" t="n">
-        <v>0.9304807585466727</v>
-      </c>
-      <c r="S44" t="n">
-        <v>0.01216182612242353</v>
-      </c>
-      <c r="T44" t="n">
-        <v>0.0002721508891694923</v>
-      </c>
-      <c r="U44" t="n">
-        <v>1997</v>
-      </c>
-      <c r="V44" t="n">
-        <v>0.000118750239778398</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.18750239778398</v>
-      </c>
-      <c r="X44" t="n">
-        <v>1.18750239778398</v>
+        <v>164.5081871375253</v>
       </c>
     </row>
     <row r="45">
@@ -3859,46 +2787,22 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>0.001749906585270956</v>
+        <v>0.007474453250571418</v>
       </c>
       <c r="L45" t="n">
-        <v>17.49906585270956</v>
+        <v>74.74453250571418</v>
       </c>
       <c r="M45" t="n">
-        <v>0.006869217290774895</v>
+        <v>0.02939118202930222</v>
       </c>
       <c r="N45" t="n">
-        <v>457.2349374690158</v>
+        <v>0.005804453250571418</v>
       </c>
       <c r="O45" t="n">
-        <v>3.111589684943077</v>
+        <v>58.04453250571417</v>
       </c>
       <c r="P45" t="n">
-        <v>457.2349374690158</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>0.007386927238382313</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0.9256237496009577</v>
-      </c>
-      <c r="S45" t="n">
-        <v>0.05785911046037873</v>
-      </c>
-      <c r="T45" t="n">
-        <v>0.001394296633769911</v>
-      </c>
-      <c r="U45" t="n">
-        <v>1722</v>
-      </c>
-      <c r="V45" t="n">
-        <v>7.990658527095586e-05</v>
-      </c>
-      <c r="W45" t="n">
-        <v>0.7990658527095569</v>
-      </c>
-      <c r="X45" t="n">
-        <v>0.7990658527095569</v>
+        <v>58.04453250571417</v>
       </c>
     </row>
     <row r="46">
@@ -3935,46 +2839,22 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>0.0002524703647133825</v>
+        <v>0.002082643898749508</v>
       </c>
       <c r="L46" t="n">
-        <v>2.524703647133825</v>
+        <v>20.82643898749508</v>
       </c>
       <c r="M46" t="n">
-        <v>0.001796783544171655</v>
+        <v>0.01481007392689626</v>
       </c>
       <c r="N46" t="n">
-        <v>430.1340093227036</v>
+        <v>0.000312643898749508</v>
       </c>
       <c r="O46" t="n">
-        <v>5.641249242531255</v>
+        <v>3.126438987495078</v>
       </c>
       <c r="P46" t="n">
-        <v>430.1340093227036</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>0.001937279958555964</v>
-      </c>
-      <c r="R46" t="n">
-        <v>0.9256237496009577</v>
-      </c>
-      <c r="S46" t="n">
-        <v>0.02072380981511853</v>
-      </c>
-      <c r="T46" t="n">
-        <v>0.0004994051590871706</v>
-      </c>
-      <c r="U46" t="n">
-        <v>1722</v>
-      </c>
-      <c r="V46" t="n">
-        <v>-0.001517529635286617</v>
-      </c>
-      <c r="W46" t="n">
-        <v>-15.17529635286617</v>
-      </c>
-      <c r="X46" t="n">
-        <v>15.17529635286617</v>
+        <v>3.126438987495078</v>
       </c>
     </row>
     <row r="47">
@@ -4011,46 +2891,22 @@
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>0.005741333835825286</v>
+        <v>0.06605303516308718</v>
       </c>
       <c r="L47" t="n">
-        <v>57.41333835825286</v>
+        <v>660.5303516308718</v>
       </c>
       <c r="M47" t="n">
-        <v>0.002189557548033359</v>
+        <v>0.02517838570966697</v>
       </c>
       <c r="N47" t="n">
-        <v>232.9512626671056</v>
+        <v>0.06269303516308718</v>
       </c>
       <c r="O47" t="n">
-        <v>0.9559463037291251</v>
+        <v>626.9303516308718</v>
       </c>
       <c r="P47" t="n">
-        <v>232.9512626671056</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>0.002263457019794845</v>
-      </c>
-      <c r="R47" t="n">
-        <v>0.9703462697836946</v>
-      </c>
-      <c r="S47" t="n">
-        <v>0.003380026776609437</v>
-      </c>
-      <c r="T47" t="n">
-        <v>7.557969638268196e-05</v>
-      </c>
-      <c r="U47" t="n">
-        <v>2000</v>
-      </c>
-      <c r="V47" t="n">
-        <v>0.002381333835825286</v>
-      </c>
-      <c r="W47" t="n">
-        <v>23.81333835825286</v>
-      </c>
-      <c r="X47" t="n">
-        <v>23.81333835825286</v>
+        <v>626.9303516308718</v>
       </c>
     </row>
     <row r="48">
@@ -4087,46 +2943,22 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>7.312206138953424e-05</v>
+        <v>0.0237606792004669</v>
       </c>
       <c r="L48" t="n">
-        <v>0.7312206138953424</v>
+        <v>237.606792004669</v>
       </c>
       <c r="M48" t="n">
-        <v>0.0001302207699539775</v>
+        <v>0.04232952820691679</v>
       </c>
       <c r="N48" t="n">
-        <v>337.8066091293396</v>
+        <v>0.0212906792004669</v>
       </c>
       <c r="O48" t="n">
-        <v>4.46397513565691</v>
+        <v>212.906792004669</v>
       </c>
       <c r="P48" t="n">
-        <v>337.8066091293396</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>0.0001345787334680881</v>
-      </c>
-      <c r="R48" t="n">
-        <v>0.9703462697836946</v>
-      </c>
-      <c r="S48" t="n">
-        <v>0.002063276233204315</v>
-      </c>
-      <c r="T48" t="n">
-        <v>4.613625913804556e-05</v>
-      </c>
-      <c r="U48" t="n">
-        <v>2000</v>
-      </c>
-      <c r="V48" t="n">
-        <v>-0.002396877938610466</v>
-      </c>
-      <c r="W48" t="n">
-        <v>-23.96877938610466</v>
-      </c>
-      <c r="X48" t="n">
-        <v>23.96877938610466</v>
+        <v>212.906792004669</v>
       </c>
     </row>
     <row r="49">
@@ -4163,46 +2995,22 @@
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>2.00118159448251e-05</v>
+        <v>0.00685172252868071</v>
       </c>
       <c r="L49" t="n">
-        <v>0.200118159448251</v>
+        <v>68.51722528680709</v>
       </c>
       <c r="M49" t="n">
-        <v>6.46587215869904e-05</v>
+        <v>0.0221312578312788</v>
       </c>
       <c r="N49" t="n">
-        <v>391.6042168187078</v>
+        <v>0.00471172252868071</v>
       </c>
       <c r="O49" t="n">
-        <v>8.098984129091761</v>
+        <v>47.11722528680709</v>
       </c>
       <c r="P49" t="n">
-        <v>391.6042168187078</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>6.698127271828292e-05</v>
-      </c>
-      <c r="R49" t="n">
-        <v>0.9703462697836946</v>
-      </c>
-      <c r="S49" t="n">
-        <v>0.001215466736256192</v>
-      </c>
-      <c r="T49" t="n">
-        <v>2.717866246658654e-05</v>
-      </c>
-      <c r="U49" t="n">
-        <v>2000</v>
-      </c>
-      <c r="V49" t="n">
-        <v>-0.002119988184055175</v>
-      </c>
-      <c r="W49" t="n">
-        <v>-21.19988184055175</v>
-      </c>
-      <c r="X49" t="n">
-        <v>21.19988184055175</v>
+        <v>47.11722528680709</v>
       </c>
     </row>
     <row r="50">
@@ -4239,46 +3047,22 @@
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>0.0009743465409303354</v>
+        <v>0.02638632656148272</v>
       </c>
       <c r="L50" t="n">
-        <v>9.743465409303354</v>
+        <v>263.8632656148272</v>
       </c>
       <c r="M50" t="n">
-        <v>0.0007191741863949446</v>
+        <v>0.01946367497636546</v>
       </c>
       <c r="N50" t="n">
-        <v>400.4437965714274</v>
+        <v>0.02410632656148272</v>
       </c>
       <c r="O50" t="n">
-        <v>0.8274191631972959</v>
+        <v>241.0632656148272</v>
       </c>
       <c r="P50" t="n">
-        <v>400.4437965714274</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>0.0007364025043344754</v>
-      </c>
-      <c r="R50" t="n">
-        <v>0.9156066370359754</v>
-      </c>
-      <c r="S50" t="n">
-        <v>0.01693353591538584</v>
-      </c>
-      <c r="T50" t="n">
-        <v>0.0003789296779748272</v>
-      </c>
-      <c r="U50" t="n">
-        <v>1997</v>
-      </c>
-      <c r="V50" t="n">
-        <v>-0.001305653459069665</v>
-      </c>
-      <c r="W50" t="n">
-        <v>-13.05653459069665</v>
-      </c>
-      <c r="X50" t="n">
-        <v>13.05653459069665</v>
+        <v>241.0632656148272</v>
       </c>
     </row>
     <row r="51">
@@ -4315,46 +3099,22 @@
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>0.0003161355830616243</v>
+        <v>0.00881703070851662</v>
       </c>
       <c r="L51" t="n">
-        <v>3.161355830616243</v>
+        <v>88.1703070851662</v>
       </c>
       <c r="M51" t="n">
-        <v>0.001072034813177002</v>
+        <v>0.02985919061225769</v>
       </c>
       <c r="N51" t="n">
-        <v>440.2056141862316</v>
+        <v>0.00688703070851662</v>
       </c>
       <c r="O51" t="n">
-        <v>3.801372596743469</v>
+        <v>68.8703070851662</v>
       </c>
       <c r="P51" t="n">
-        <v>440.2056141862316</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>0.001136487132069982</v>
-      </c>
-      <c r="R51" t="n">
-        <v>0.9139459120072527</v>
-      </c>
-      <c r="S51" t="n">
-        <v>0.02350954449528336</v>
-      </c>
-      <c r="T51" t="n">
-        <v>0.0005396300309209184</v>
-      </c>
-      <c r="U51" t="n">
-        <v>1898</v>
-      </c>
-      <c r="V51" t="n">
-        <v>-0.001613864416938376</v>
-      </c>
-      <c r="W51" t="n">
-        <v>-16.13864416938376</v>
-      </c>
-      <c r="X51" t="n">
-        <v>16.13864416938376</v>
+        <v>68.8703070851662</v>
       </c>
     </row>
     <row r="52">
@@ -4391,46 +3151,22 @@
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>5.028210339699932e-05</v>
+        <v>0.002246100198627726</v>
       </c>
       <c r="L52" t="n">
-        <v>0.5028210339699932</v>
+        <v>22.46100198627726</v>
       </c>
       <c r="M52" t="n">
-        <v>0.0003058965622699186</v>
+        <v>0.01366345777694287</v>
       </c>
       <c r="N52" t="n">
-        <v>455.1563030936441</v>
+        <v>0.0003761001986277263</v>
       </c>
       <c r="O52" t="n">
-        <v>6.81971289511144</v>
+        <v>3.761001986277265</v>
       </c>
       <c r="P52" t="n">
-        <v>455.1563030936441</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>0.0003207588998123198</v>
-      </c>
-      <c r="R52" t="n">
-        <v>0.9138987306787979</v>
-      </c>
-      <c r="S52" t="n">
-        <v>0.009484835631538494</v>
-      </c>
-      <c r="T52" t="n">
-        <v>0.0002178264645270775</v>
-      </c>
-      <c r="U52" t="n">
-        <v>1896</v>
-      </c>
-      <c r="V52" t="n">
-        <v>-0.001819717896603001</v>
-      </c>
-      <c r="W52" t="n">
-        <v>-18.19717896603001</v>
-      </c>
-      <c r="X52" t="n">
-        <v>18.19717896603001</v>
+        <v>3.761001986277265</v>
       </c>
     </row>
     <row r="53">
@@ -4467,46 +3203,22 @@
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>0.001844884739758291</v>
+        <v>0.01810777332051252</v>
       </c>
       <c r="L53" t="n">
-        <v>18.44884739758291</v>
+        <v>181.0777332051252</v>
       </c>
       <c r="M53" t="n">
-        <v>0.001538570023358479</v>
+        <v>0.01511209594124734</v>
       </c>
       <c r="N53" t="n">
-        <v>486.4724918232947</v>
+        <v>0.01641777332051252</v>
       </c>
       <c r="O53" t="n">
-        <v>0.661055559888678</v>
+        <v>164.1777332051252</v>
       </c>
       <c r="P53" t="n">
-        <v>486.4724918232947</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>0.001525754878733817</v>
-      </c>
-      <c r="R53" t="n">
-        <v>0.9190459506462362</v>
-      </c>
-      <c r="S53" t="n">
-        <v>0.012227672308299</v>
-      </c>
-      <c r="T53" t="n">
-        <v>0.0002737614808744971</v>
-      </c>
-      <c r="U53" t="n">
-        <v>1995</v>
-      </c>
-      <c r="V53" t="n">
-        <v>0.0001548847397582907</v>
-      </c>
-      <c r="W53" t="n">
-        <v>1.548847397582907</v>
-      </c>
-      <c r="X53" t="n">
-        <v>1.548847397582907</v>
+        <v>164.1777332051252</v>
       </c>
     </row>
     <row r="54">
@@ -4543,46 +3255,22 @@
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>0.001322315935676165</v>
+        <v>0.007153769473852553</v>
       </c>
       <c r="L54" t="n">
-        <v>13.22315935676165</v>
+        <v>71.53769473852553</v>
       </c>
       <c r="M54" t="n">
-        <v>0.005035162599662591</v>
+        <v>0.02728195204608923</v>
       </c>
       <c r="N54" t="n">
-        <v>473.9855713328167</v>
+        <v>0.005553769473852554</v>
       </c>
       <c r="O54" t="n">
-        <v>3.018340298367971</v>
+        <v>55.53769473852553</v>
       </c>
       <c r="P54" t="n">
-        <v>473.9855713328167</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>0.005452029030132777</v>
-      </c>
-      <c r="R54" t="n">
-        <v>0.9142856041590049</v>
-      </c>
-      <c r="S54" t="n">
-        <v>0.04792070388711832</v>
-      </c>
-      <c r="T54" t="n">
-        <v>0.00115479957410421</v>
-      </c>
-      <c r="U54" t="n">
-        <v>1722</v>
-      </c>
-      <c r="V54" t="n">
-        <v>-0.0002776840643238352</v>
-      </c>
-      <c r="W54" t="n">
-        <v>-2.776840643238351</v>
-      </c>
-      <c r="X54" t="n">
-        <v>2.776840643238351</v>
+        <v>55.53769473852553</v>
       </c>
     </row>
     <row r="55">
@@ -4619,46 +3307,22 @@
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>0.0002187282464283326</v>
+        <v>0.001704944367390888</v>
       </c>
       <c r="L55" t="n">
-        <v>2.187282464283326</v>
+        <v>17.04944367390888</v>
       </c>
       <c r="M55" t="n">
-        <v>0.001505546488294514</v>
+        <v>0.01170789794992074</v>
       </c>
       <c r="N55" t="n">
-        <v>444.7357830491152</v>
+        <v>5.494436739088759e-05</v>
       </c>
       <c r="O55" t="n">
-        <v>5.456061201338827</v>
+        <v>0.5494436739088755</v>
       </c>
       <c r="P55" t="n">
-        <v>444.7357830491152</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>0.001656355252821832</v>
-      </c>
-      <c r="R55" t="n">
-        <v>0.9142856041590049</v>
-      </c>
-      <c r="S55" t="n">
-        <v>0.01840274191339292</v>
-      </c>
-      <c r="T55" t="n">
-        <v>0.0004434717522930312</v>
-      </c>
-      <c r="U55" t="n">
-        <v>1722</v>
-      </c>
-      <c r="V55" t="n">
-        <v>-0.001431271753571667</v>
-      </c>
-      <c r="W55" t="n">
-        <v>-14.31271753571667</v>
-      </c>
-      <c r="X55" t="n">
-        <v>14.31271753571667</v>
+        <v>0.5494436739088755</v>
       </c>
     </row>
     <row r="56">
@@ -4695,46 +3359,22 @@
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>0.00564549610230604</v>
+        <v>0.06619262033061582</v>
       </c>
       <c r="L56" t="n">
-        <v>56.4549610230604</v>
+        <v>661.9262033061582</v>
       </c>
       <c r="M56" t="n">
-        <v>0.002153721565795215</v>
+        <v>0.02522694808757193</v>
       </c>
       <c r="N56" t="n">
-        <v>230.3934583762056</v>
+        <v>0.06283262033061582</v>
       </c>
       <c r="O56" t="n">
-        <v>0.9562630590249905</v>
+        <v>628.3262033061582</v>
       </c>
       <c r="P56" t="n">
-        <v>230.3934583762056</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>0.00222556593635695</v>
-      </c>
-      <c r="R56" t="n">
-        <v>0.9707554723685682</v>
-      </c>
-      <c r="S56" t="n">
-        <v>0.003370172254616945</v>
-      </c>
-      <c r="T56" t="n">
-        <v>7.535934257207219e-05</v>
-      </c>
-      <c r="U56" t="n">
-        <v>2000</v>
-      </c>
-      <c r="V56" t="n">
-        <v>0.00228549610230604</v>
-      </c>
-      <c r="W56" t="n">
-        <v>22.8549610230604</v>
-      </c>
-      <c r="X56" t="n">
-        <v>22.8549610230604</v>
+        <v>628.3262033061582</v>
       </c>
     </row>
     <row r="57">
@@ -4771,46 +3411,22 @@
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>9.871083243731149e-05</v>
+        <v>0.02463983979143117</v>
       </c>
       <c r="L57" t="n">
-        <v>0.9871083243731149</v>
+        <v>246.3983979143117</v>
       </c>
       <c r="M57" t="n">
-        <v>0.0001761891646705893</v>
+        <v>0.04397222856247596</v>
       </c>
       <c r="N57" t="n">
-        <v>328.7562087511653</v>
+        <v>0.02209983979143117</v>
       </c>
       <c r="O57" t="n">
-        <v>4.474085882391785</v>
+        <v>220.9983979143117</v>
       </c>
       <c r="P57" t="n">
-        <v>328.7562087511653</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>0.0001821012065654824</v>
-      </c>
-      <c r="R57" t="n">
-        <v>0.9707554723685682</v>
-      </c>
-      <c r="S57" t="n">
-        <v>0.002444346314998918</v>
-      </c>
-      <c r="T57" t="n">
-        <v>5.465724520888694e-05</v>
-      </c>
-      <c r="U57" t="n">
-        <v>2000</v>
-      </c>
-      <c r="V57" t="n">
-        <v>-0.002441289167562688</v>
-      </c>
-      <c r="W57" t="n">
-        <v>-24.41289167562688</v>
-      </c>
-      <c r="X57" t="n">
-        <v>24.41289167562688</v>
+        <v>220.9983979143117</v>
       </c>
     </row>
     <row r="58">
@@ -4847,46 +3463,22 @@
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>3.000045246132142e-05</v>
+        <v>0.007234263659741408</v>
       </c>
       <c r="L58" t="n">
-        <v>0.3000045246132142</v>
+        <v>72.34263659741407</v>
       </c>
       <c r="M58" t="n">
-        <v>9.741815079377267e-05</v>
+        <v>0.02347572615180013</v>
       </c>
       <c r="N58" t="n">
-        <v>380.4912154051598</v>
+        <v>0.005014263659741408</v>
       </c>
       <c r="O58" t="n">
-        <v>8.139580279889593</v>
+        <v>50.14263659741407</v>
       </c>
       <c r="P58" t="n">
-        <v>380.4912154051598</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>0.0001009111868660004</v>
-      </c>
-      <c r="R58" t="n">
-        <v>0.9707554723685682</v>
-      </c>
-      <c r="S58" t="n">
-        <v>0.001559011094790312</v>
-      </c>
-      <c r="T58" t="n">
-        <v>3.486054785627505e-05</v>
-      </c>
-      <c r="U58" t="n">
-        <v>2000</v>
-      </c>
-      <c r="V58" t="n">
-        <v>-0.002189999547538678</v>
-      </c>
-      <c r="W58" t="n">
-        <v>-21.89999547538678</v>
-      </c>
-      <c r="X58" t="n">
-        <v>21.89999547538678</v>
+        <v>50.14263659741407</v>
       </c>
     </row>
     <row r="59">
@@ -4923,46 +3515,22 @@
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>0.0009858155838688668</v>
+        <v>0.02542898042973864</v>
       </c>
       <c r="L59" t="n">
-        <v>9.858155838688669</v>
+        <v>254.2898042973864</v>
       </c>
       <c r="M59" t="n">
-        <v>0.0007309701070494615</v>
+        <v>0.01883732854348387</v>
       </c>
       <c r="N59" t="n">
-        <v>388.4049900774456</v>
+        <v>0.02309898042973864</v>
       </c>
       <c r="O59" t="n">
-        <v>0.8312063831213847</v>
+        <v>230.9898042973864</v>
       </c>
       <c r="P59" t="n">
-        <v>388.4049900774456</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>0.0007485806665291979</v>
-      </c>
-      <c r="R59" t="n">
-        <v>0.9169429496140368</v>
-      </c>
-      <c r="S59" t="n">
-        <v>0.01869844760716969</v>
-      </c>
-      <c r="T59" t="n">
-        <v>0.0004186336187238783</v>
-      </c>
-      <c r="U59" t="n">
-        <v>1995</v>
-      </c>
-      <c r="V59" t="n">
-        <v>-0.001344184416131133</v>
-      </c>
-      <c r="W59" t="n">
-        <v>-13.44184416131133</v>
-      </c>
-      <c r="X59" t="n">
-        <v>13.44184416131133</v>
+        <v>230.9898042973864</v>
       </c>
     </row>
     <row r="60">
@@ -4999,46 +3567,22 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>0.0002997923968849952</v>
+        <v>0.009351473447542507</v>
       </c>
       <c r="L60" t="n">
-        <v>2.997923968849952</v>
+        <v>93.51473447542507</v>
       </c>
       <c r="M60" t="n">
-        <v>0.001023764539348878</v>
+        <v>0.03188663829768804</v>
       </c>
       <c r="N60" t="n">
-        <v>426.8836872469093</v>
+        <v>0.007371473447542507</v>
       </c>
       <c r="O60" t="n">
-        <v>3.828109925623891</v>
+        <v>73.71473447542508</v>
       </c>
       <c r="P60" t="n">
-        <v>426.8836872469093</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>0.001087669158281049</v>
-      </c>
-      <c r="R60" t="n">
-        <v>0.9154378619907864</v>
-      </c>
-      <c r="S60" t="n">
-        <v>0.02324519415172149</v>
-      </c>
-      <c r="T60" t="n">
-        <v>0.0005330008745360234</v>
-      </c>
-      <c r="U60" t="n">
-        <v>1902</v>
-      </c>
-      <c r="V60" t="n">
-        <v>-0.001680207603115005</v>
-      </c>
-      <c r="W60" t="n">
-        <v>-16.80207603115005</v>
-      </c>
-      <c r="X60" t="n">
-        <v>16.80207603115005</v>
+        <v>73.71473447542508</v>
       </c>
     </row>
     <row r="61">
@@ -5075,46 +3619,22 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>5.26975108427462e-05</v>
+        <v>0.002450620431855744</v>
       </c>
       <c r="L61" t="n">
-        <v>0.5269751084274621</v>
+        <v>24.50620431855744</v>
       </c>
       <c r="M61" t="n">
-        <v>0.0003238657048502921</v>
+        <v>0.01505622769894044</v>
       </c>
       <c r="N61" t="n">
-        <v>441.0590122197753</v>
+        <v>0.0005606204318557447</v>
       </c>
       <c r="O61" t="n">
-        <v>6.889374476890616</v>
+        <v>5.606204318557445</v>
       </c>
       <c r="P61" t="n">
-        <v>441.0590122197753</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>0.0003390260582725043</v>
-      </c>
-      <c r="R61" t="n">
-        <v>0.9154378619907864</v>
-      </c>
-      <c r="S61" t="n">
-        <v>0.01004463439717839</v>
-      </c>
-      <c r="T61" t="n">
-        <v>0.0002303185287740095</v>
-      </c>
-      <c r="U61" t="n">
-        <v>1902</v>
-      </c>
-      <c r="V61" t="n">
-        <v>-0.001837302489157254</v>
-      </c>
-      <c r="W61" t="n">
-        <v>-18.37302489157254</v>
-      </c>
-      <c r="X61" t="n">
-        <v>18.37302489157254</v>
+        <v>5.606204318557445</v>
       </c>
     </row>
     <row r="62">
@@ -5151,46 +3671,22 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>0.001877061768274877</v>
+        <v>0.02049618488889091</v>
       </c>
       <c r="L62" t="n">
-        <v>18.77061768274877</v>
+        <v>204.9618488889091</v>
       </c>
       <c r="M62" t="n">
-        <v>0.001583248415148491</v>
+        <v>0.01729614000780809</v>
       </c>
       <c r="N62" t="n">
-        <v>470.9042991842774</v>
+        <v>0.01878618488889091</v>
       </c>
       <c r="O62" t="n">
-        <v>0.668590854995302</v>
+        <v>187.8618488889091</v>
       </c>
       <c r="P62" t="n">
-        <v>470.9042991842774</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>0.001566892378630657</v>
-      </c>
-      <c r="R62" t="n">
-        <v>0.9209842797993403</v>
-      </c>
-      <c r="S62" t="n">
-        <v>0.01228467650728952</v>
-      </c>
-      <c r="T62" t="n">
-        <v>0.0002750377298234582</v>
-      </c>
-      <c r="U62" t="n">
-        <v>1995</v>
-      </c>
-      <c r="V62" t="n">
-        <v>0.0001670617682748771</v>
-      </c>
-      <c r="W62" t="n">
-        <v>1.670617682748773</v>
-      </c>
-      <c r="X62" t="n">
-        <v>1.670617682748773</v>
+        <v>187.8618488889091</v>
       </c>
     </row>
     <row r="63">
@@ -5227,46 +3723,22 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>0.001333393373959446</v>
+        <v>0.007246441599802063</v>
       </c>
       <c r="L63" t="n">
-        <v>13.33393373959446</v>
+        <v>72.46441599802063</v>
       </c>
       <c r="M63" t="n">
-        <v>0.005149549308054349</v>
+        <v>0.02801853590966989</v>
       </c>
       <c r="N63" t="n">
-        <v>458.7852496353289</v>
+        <v>0.005646441599802063</v>
       </c>
       <c r="O63" t="n">
-        <v>3.061264551266725</v>
+        <v>56.46441599802063</v>
       </c>
       <c r="P63" t="n">
-        <v>458.7852496353289</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>0.005575160461630251</v>
-      </c>
-      <c r="R63" t="n">
-        <v>0.9163504563825546</v>
-      </c>
-      <c r="S63" t="n">
-        <v>0.04801268890876432</v>
-      </c>
-      <c r="T63" t="n">
-        <v>0.001156680436500122</v>
-      </c>
-      <c r="U63" t="n">
-        <v>1723</v>
-      </c>
-      <c r="V63" t="n">
-        <v>-0.0002666066260405538</v>
-      </c>
-      <c r="W63" t="n">
-        <v>-2.666066260405538</v>
-      </c>
-      <c r="X63" t="n">
-        <v>2.666066260405538</v>
+        <v>56.46441599802063</v>
       </c>
     </row>
     <row r="64">
@@ -5303,46 +3775,22 @@
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>0.0002093259323662232</v>
+        <v>0.001851475240026038</v>
       </c>
       <c r="L64" t="n">
-        <v>2.093259323662232</v>
+        <v>18.51475240026038</v>
       </c>
       <c r="M64" t="n">
-        <v>0.001465642653697844</v>
+        <v>0.01293129054814663</v>
       </c>
       <c r="N64" t="n">
-        <v>430.5512276332965</v>
+        <v>0.0002014752400260377</v>
       </c>
       <c r="O64" t="n">
-        <v>5.550025715661102</v>
+        <v>2.014752400260377</v>
       </c>
       <c r="P64" t="n">
-        <v>430.5512276332965</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>0.001615108030581994</v>
-      </c>
-      <c r="R64" t="n">
-        <v>0.9162995730317872</v>
-      </c>
-      <c r="S64" t="n">
-        <v>0.018031241007174</v>
-      </c>
-      <c r="T64" t="n">
-        <v>0.0004345192734377225</v>
-      </c>
-      <c r="U64" t="n">
-        <v>1722</v>
-      </c>
-      <c r="V64" t="n">
-        <v>-0.001440674067633777</v>
-      </c>
-      <c r="W64" t="n">
-        <v>-14.40674067633777</v>
-      </c>
-      <c r="X64" t="n">
-        <v>14.40674067633777</v>
+        <v>2.014752400260377</v>
       </c>
     </row>
     <row r="65">
@@ -5379,46 +3827,22 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>0.006221119841872998</v>
+        <v>0.06763555528612387</v>
       </c>
       <c r="L65" t="n">
-        <v>62.21119841872998</v>
+        <v>676.3555528612387</v>
       </c>
       <c r="M65" t="n">
-        <v>0.002382015454131239</v>
+        <v>0.025864380171401</v>
       </c>
       <c r="N65" t="n">
-        <v>211.3515503555101</v>
+        <v>0.06332555528612388</v>
       </c>
       <c r="O65" t="n">
-        <v>0.9597672830131053</v>
+        <v>633.2555528612387</v>
       </c>
       <c r="P65" t="n">
-        <v>211.3515503555101</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>0.002457164497422637</v>
-      </c>
-      <c r="R65" t="n">
-        <v>0.9724739422924106</v>
-      </c>
-      <c r="S65" t="n">
-        <v>0.003574759034947564</v>
-      </c>
-      <c r="T65" t="n">
-        <v>7.993404205324299e-05</v>
-      </c>
-      <c r="U65" t="n">
-        <v>2000</v>
-      </c>
-      <c r="V65" t="n">
-        <v>0.001911119841872998</v>
-      </c>
-      <c r="W65" t="n">
-        <v>19.11119841872998</v>
-      </c>
-      <c r="X65" t="n">
-        <v>19.11119841872998</v>
+        <v>633.2555528612387</v>
       </c>
     </row>
     <row r="66">
@@ -5455,46 +3879,22 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>0.0001665371085887361</v>
+        <v>0.02631550212464251</v>
       </c>
       <c r="L66" t="n">
-        <v>1.665371085887361</v>
+        <v>263.1550212464251</v>
       </c>
       <c r="M66" t="n">
-        <v>0.000299661621497764</v>
+        <v>0.04730950802246982</v>
       </c>
       <c r="N66" t="n">
-        <v>306.7753277785879</v>
+        <v>0.02333550212464251</v>
       </c>
       <c r="O66" t="n">
-        <v>4.510347871614676</v>
+        <v>233.3550212464251</v>
       </c>
       <c r="P66" t="n">
-        <v>306.7753277785879</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>0.0003090635699195876</v>
-      </c>
-      <c r="R66" t="n">
-        <v>0.9724739422924106</v>
-      </c>
-      <c r="S66" t="n">
-        <v>0.003825163212845742</v>
-      </c>
-      <c r="T66" t="n">
-        <v>8.553324968954575e-05</v>
-      </c>
-      <c r="U66" t="n">
-        <v>2000</v>
-      </c>
-      <c r="V66" t="n">
-        <v>-0.002813462891411264</v>
-      </c>
-      <c r="W66" t="n">
-        <v>-28.13462891411264</v>
-      </c>
-      <c r="X66" t="n">
-        <v>28.13462891411264</v>
+        <v>233.3550212464251</v>
       </c>
     </row>
     <row r="67">
@@ -5531,46 +3931,22 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>3.743601463137912e-05</v>
+        <v>0.007716125554306381</v>
       </c>
       <c r="L67" t="n">
-        <v>0.3743601463137912</v>
+        <v>77.16125554306382</v>
       </c>
       <c r="M67" t="n">
-        <v>0.0001230633221968902</v>
+        <v>0.02533229541542268</v>
       </c>
       <c r="N67" t="n">
-        <v>361.0599572301984</v>
+        <v>0.005266125554306381</v>
       </c>
       <c r="O67" t="n">
-        <v>8.24003318799285</v>
+        <v>52.66125554306382</v>
       </c>
       <c r="P67" t="n">
-        <v>361.0599572301984</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>0.0001272963133112431</v>
-      </c>
-      <c r="R67" t="n">
-        <v>0.9724739422924106</v>
-      </c>
-      <c r="S67" t="n">
-        <v>0.001795924330483156</v>
-      </c>
-      <c r="T67" t="n">
-        <v>4.015808885406134e-05</v>
-      </c>
-      <c r="U67" t="n">
-        <v>2000</v>
-      </c>
-      <c r="V67" t="n">
-        <v>-0.002412563985368621</v>
-      </c>
-      <c r="W67" t="n">
-        <v>-24.12563985368621</v>
-      </c>
-      <c r="X67" t="n">
-        <v>24.12563985368621</v>
+        <v>52.66125554306382</v>
       </c>
     </row>
     <row r="68">
@@ -5607,46 +3983,22 @@
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>0.0003654335600286464</v>
+        <v>0.02623851790174057</v>
       </c>
       <c r="L68" t="n">
-        <v>3.654335600286464</v>
+        <v>262.3851790174057</v>
       </c>
       <c r="M68" t="n">
-        <v>0.000274380650204625</v>
+        <v>0.0196633961169748</v>
       </c>
       <c r="N68" t="n">
-        <v>368.2176038889041</v>
+        <v>0.02367851790174057</v>
       </c>
       <c r="O68" t="n">
-        <v>0.841685768666632</v>
+        <v>236.7851790174057</v>
       </c>
       <c r="P68" t="n">
-        <v>368.2176038889041</v>
-      </c>
-      <c r="Q68" t="n">
-        <v>0.000275886165403731</v>
-      </c>
-      <c r="R68" t="n">
-        <v>0.9228746750647605</v>
-      </c>
-      <c r="S68" t="n">
-        <v>0.004180789177908886</v>
-      </c>
-      <c r="T68" t="n">
-        <v>9.357891376406629e-05</v>
-      </c>
-      <c r="U68" t="n">
-        <v>1996</v>
-      </c>
-      <c r="V68" t="n">
-        <v>-0.002194566439971354</v>
-      </c>
-      <c r="W68" t="n">
-        <v>-21.94566439971354</v>
-      </c>
-      <c r="X68" t="n">
-        <v>21.94566439971354</v>
+        <v>236.7851790174057</v>
       </c>
     </row>
     <row r="69">
@@ -5683,46 +4035,22 @@
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>0.0005301761529095553</v>
+        <v>0.00967015994609915</v>
       </c>
       <c r="L69" t="n">
-        <v>5.301761529095553</v>
+        <v>96.7015994609915</v>
       </c>
       <c r="M69" t="n">
-        <v>0.001839223956261321</v>
+        <v>0.03347324845802394</v>
       </c>
       <c r="N69" t="n">
-        <v>409.1243745528142</v>
+        <v>0.00757015994609915</v>
       </c>
       <c r="O69" t="n">
-        <v>3.888833574750381</v>
+        <v>75.7015994609915</v>
       </c>
       <c r="P69" t="n">
-        <v>409.1243745528142</v>
-      </c>
-      <c r="Q69" t="n">
-        <v>0.001954496145919369</v>
-      </c>
-      <c r="R69" t="n">
-        <v>0.921227737896132</v>
-      </c>
-      <c r="S69" t="n">
-        <v>0.03206522659864693</v>
-      </c>
-      <c r="T69" t="n">
-        <v>0.0007367910233233937</v>
-      </c>
-      <c r="U69" t="n">
-        <v>1894</v>
-      </c>
-      <c r="V69" t="n">
-        <v>-0.001569823847090445</v>
-      </c>
-      <c r="W69" t="n">
-        <v>-15.69823847090445</v>
-      </c>
-      <c r="X69" t="n">
-        <v>15.69823847090445</v>
+        <v>75.7015994609915</v>
       </c>
     </row>
     <row r="70">
@@ -5759,46 +4087,22 @@
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>4.66494547502817e-05</v>
+        <v>0.002846460207847353</v>
       </c>
       <c r="L70" t="n">
-        <v>0.4664945475028169</v>
+        <v>28.46460207847353</v>
       </c>
       <c r="M70" t="n">
-        <v>0.0002922400868435282</v>
+        <v>0.01782186628109097</v>
       </c>
       <c r="N70" t="n">
-        <v>424.5491788612061</v>
+        <v>0.0008464602078473529</v>
       </c>
       <c r="O70" t="n">
-        <v>7.022603494963474</v>
+        <v>8.464602078473529</v>
       </c>
       <c r="P70" t="n">
-        <v>424.5491788612061</v>
-      </c>
-      <c r="Q70" t="n">
-        <v>0.0003040927632815865</v>
-      </c>
-      <c r="R70" t="n">
-        <v>0.921227737896132</v>
-      </c>
-      <c r="S70" t="n">
-        <v>0.009041082788584948</v>
-      </c>
-      <c r="T70" t="n">
-        <v>0.0002077449419937709</v>
-      </c>
-      <c r="U70" t="n">
-        <v>1894</v>
-      </c>
-      <c r="V70" t="n">
-        <v>-0.001953350545249718</v>
-      </c>
-      <c r="W70" t="n">
-        <v>-19.53350545249718</v>
-      </c>
-      <c r="X70" t="n">
-        <v>19.53350545249718</v>
+        <v>8.464602078473529</v>
       </c>
     </row>
     <row r="71">
@@ -5835,46 +4139,22 @@
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>0.001910890630472197</v>
+        <v>0.01985873942340603</v>
       </c>
       <c r="L71" t="n">
-        <v>19.10890630472197</v>
+        <v>198.5873942340603</v>
       </c>
       <c r="M71" t="n">
-        <v>0.001645403515065806</v>
+        <v>0.01710445283594836</v>
       </c>
       <c r="N71" t="n">
-        <v>454.7581517450332</v>
+        <v>0.01802873942340603</v>
       </c>
       <c r="O71" t="n">
-        <v>0.6825375102944254</v>
+        <v>180.2873942340603</v>
       </c>
       <c r="P71" t="n">
-        <v>454.7581517450332</v>
-      </c>
-      <c r="Q71" t="n">
-        <v>0.001613567774236267</v>
-      </c>
-      <c r="R71" t="n">
-        <v>0.9290280619375395</v>
-      </c>
-      <c r="S71" t="n">
-        <v>0.01230880831698986</v>
-      </c>
-      <c r="T71" t="n">
-        <v>0.0002755089680485005</v>
-      </c>
-      <c r="U71" t="n">
-        <v>1996</v>
-      </c>
-      <c r="V71" t="n">
-        <v>8.089063047219736e-05</v>
-      </c>
-      <c r="W71" t="n">
-        <v>0.8089063047219724</v>
-      </c>
-      <c r="X71" t="n">
-        <v>0.8089063047219724</v>
+        <v>180.2873942340603</v>
       </c>
     </row>
     <row r="72">
@@ -5911,46 +4191,22 @@
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>0.001794359010973361</v>
+        <v>0.007746810661290676</v>
       </c>
       <c r="L72" t="n">
-        <v>17.94359010973362</v>
+        <v>77.46810661290675</v>
       </c>
       <c r="M72" t="n">
-        <v>0.007093923706538436</v>
+        <v>0.03067102753311347</v>
       </c>
       <c r="N72" t="n">
-        <v>443.6905001469594</v>
+        <v>0.006036810661290675</v>
       </c>
       <c r="O72" t="n">
-        <v>3.133769920213094</v>
+        <v>60.36810661290675</v>
       </c>
       <c r="P72" t="n">
-        <v>443.6905001469594</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>0.007643426108144384</v>
-      </c>
-      <c r="R72" t="n">
-        <v>0.9240502977936662</v>
-      </c>
-      <c r="S72" t="n">
-        <v>0.05912148326049438</v>
-      </c>
-      <c r="T72" t="n">
-        <v>0.001425131324758192</v>
-      </c>
-      <c r="U72" t="n">
-        <v>1721</v>
-      </c>
-      <c r="V72" t="n">
-        <v>8.435901097336132e-05</v>
-      </c>
-      <c r="W72" t="n">
-        <v>0.8435901097336149</v>
-      </c>
-      <c r="X72" t="n">
-        <v>0.8435901097336149</v>
+        <v>60.36810661290675</v>
       </c>
     </row>
     <row r="73">
@@ -5987,46 +4243,22 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>0.0002534849409068275</v>
+        <v>0.002047404712345608</v>
       </c>
       <c r="L73" t="n">
-        <v>2.534849409068276</v>
+        <v>20.47404712345609</v>
       </c>
       <c r="M73" t="n">
-        <v>0.001821899734591041</v>
+        <v>0.01469642672490255</v>
       </c>
       <c r="N73" t="n">
-        <v>417.1077053400167</v>
+        <v>0.0002974047123456083</v>
       </c>
       <c r="O73" t="n">
-        <v>5.697210197792327</v>
+        <v>2.974047123456085</v>
       </c>
       <c r="P73" t="n">
-        <v>417.1077053400167</v>
-      </c>
-      <c r="Q73" t="n">
-        <v>0.001974478444106374</v>
-      </c>
-      <c r="R73" t="n">
-        <v>0.9239912937230306</v>
-      </c>
-      <c r="S73" t="n">
-        <v>0.02079690743597032</v>
-      </c>
-      <c r="T73" t="n">
-        <v>0.0005014579667169579</v>
-      </c>
-      <c r="U73" t="n">
-        <v>1720</v>
-      </c>
-      <c r="V73" t="n">
-        <v>-0.001496515059093173</v>
-      </c>
-      <c r="W73" t="n">
-        <v>-14.96515059093172</v>
-      </c>
-      <c r="X73" t="n">
-        <v>14.96515059093172</v>
+        <v>2.974047123456085</v>
       </c>
     </row>
     <row r="74">
@@ -6063,46 +4295,22 @@
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>0.006232604051795023</v>
+        <v>0.06767129332242586</v>
       </c>
       <c r="L74" t="n">
-        <v>62.32604051795023</v>
+        <v>676.7129332242586</v>
       </c>
       <c r="M74" t="n">
-        <v>0.002384506031490557</v>
+        <v>0.02587366405461034</v>
       </c>
       <c r="N74" t="n">
-        <v>216.1340213802533</v>
+        <v>0.06363129332242586</v>
       </c>
       <c r="O74" t="n">
-        <v>0.9590004739417002</v>
+        <v>636.3129332242586</v>
       </c>
       <c r="P74" t="n">
-        <v>216.1340213802533</v>
-      </c>
-      <c r="Q74" t="n">
-        <v>0.002461122722958295</v>
-      </c>
-      <c r="R74" t="n">
-        <v>0.9718858083557437</v>
-      </c>
-      <c r="S74" t="n">
-        <v>0.003557141802397927</v>
-      </c>
-      <c r="T74" t="n">
-        <v>7.954010875767888e-05</v>
-      </c>
-      <c r="U74" t="n">
-        <v>2000</v>
-      </c>
-      <c r="V74" t="n">
-        <v>0.002192604051795023</v>
-      </c>
-      <c r="W74" t="n">
-        <v>21.92604051795023</v>
-      </c>
-      <c r="X74" t="n">
-        <v>21.92604051795023</v>
+        <v>636.3129332242586</v>
       </c>
     </row>
     <row r="75">
@@ -6139,46 +4347,22 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>0.000127186417950204</v>
+        <v>0.02495062942995565</v>
       </c>
       <c r="L75" t="n">
-        <v>1.27186417950204</v>
+        <v>249.5062942995565</v>
       </c>
       <c r="M75" t="n">
-        <v>0.0002281891265865584</v>
+        <v>0.04475264244423923</v>
       </c>
       <c r="N75" t="n">
-        <v>316.9068236321198</v>
+        <v>0.02213062942995565</v>
       </c>
       <c r="O75" t="n">
-        <v>4.497220111106228</v>
+        <v>221.3062942995565</v>
       </c>
       <c r="P75" t="n">
-        <v>316.9068236321198</v>
-      </c>
-      <c r="Q75" t="n">
-        <v>0.0002354526740795893</v>
-      </c>
-      <c r="R75" t="n">
-        <v>0.9718858083557437</v>
-      </c>
-      <c r="S75" t="n">
-        <v>0.003233232121327328</v>
-      </c>
-      <c r="T75" t="n">
-        <v>7.229726810323753e-05</v>
-      </c>
-      <c r="U75" t="n">
-        <v>2000</v>
-      </c>
-      <c r="V75" t="n">
-        <v>-0.002692813582049796</v>
-      </c>
-      <c r="W75" t="n">
-        <v>-26.92813582049796</v>
-      </c>
-      <c r="X75" t="n">
-        <v>26.92813582049796</v>
+        <v>221.3062942995565</v>
       </c>
     </row>
     <row r="76">
@@ -6215,46 +4399,22 @@
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>2.669907095074441e-05</v>
+        <v>0.00728958069019536</v>
       </c>
       <c r="L76" t="n">
-        <v>0.2669907095074441</v>
+        <v>72.89580690195361</v>
       </c>
       <c r="M76" t="n">
-        <v>8.726776898196837e-05</v>
+        <v>0.02380200400304077</v>
       </c>
       <c r="N76" t="n">
-        <v>372.6896970068285</v>
+        <v>0.00496958069019536</v>
       </c>
       <c r="O76" t="n">
-        <v>8.193088725735944</v>
+        <v>49.6958069019536</v>
       </c>
       <c r="P76" t="n">
-        <v>372.6896970068285</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>9.029394049535145e-05</v>
-      </c>
-      <c r="R76" t="n">
-        <v>0.9718858083557437</v>
-      </c>
-      <c r="S76" t="n">
-        <v>0.001458689007954424</v>
-      </c>
-      <c r="T76" t="n">
-        <v>3.261727779817824e-05</v>
-      </c>
-      <c r="U76" t="n">
-        <v>2000</v>
-      </c>
-      <c r="V76" t="n">
-        <v>-0.002293300929049256</v>
-      </c>
-      <c r="W76" t="n">
-        <v>-22.93300929049256</v>
-      </c>
-      <c r="X76" t="n">
-        <v>22.93300929049256</v>
+        <v>49.6958069019536</v>
       </c>
     </row>
     <row r="77">
@@ -6291,46 +4451,22 @@
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>0.000364787975512511</v>
+        <v>0.02455365910844621</v>
       </c>
       <c r="L77" t="n">
-        <v>3.647879755125111</v>
+        <v>245.5365910844621</v>
       </c>
       <c r="M77" t="n">
-        <v>0.0002724387185240451</v>
+        <v>0.01830891150163376</v>
       </c>
       <c r="N77" t="n">
-        <v>380.5737818592557</v>
+        <v>0.02215365910844621</v>
       </c>
       <c r="O77" t="n">
-        <v>0.8372077627770427</v>
+        <v>221.5365910844621</v>
       </c>
       <c r="P77" t="n">
-        <v>380.5737818592557</v>
-      </c>
-      <c r="Q77" t="n">
-        <v>0.0002747970822023828</v>
-      </c>
-      <c r="R77" t="n">
-        <v>0.9208778901143818</v>
-      </c>
-      <c r="S77" t="n">
-        <v>0.004135749096905859</v>
-      </c>
-      <c r="T77" t="n">
-        <v>9.252443497447665e-05</v>
-      </c>
-      <c r="U77" t="n">
-        <v>1998</v>
-      </c>
-      <c r="V77" t="n">
-        <v>-0.002035212024487489</v>
-      </c>
-      <c r="W77" t="n">
-        <v>-20.35212024487489</v>
-      </c>
-      <c r="X77" t="n">
-        <v>20.35212024487489</v>
+        <v>221.5365910844621</v>
       </c>
     </row>
     <row r="78">
@@ -6367,46 +4503,22 @@
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>0.0004650328735445716</v>
+        <v>0.009382454194562144</v>
       </c>
       <c r="L78" t="n">
-        <v>4.650328735445716</v>
+        <v>93.82454194562145</v>
       </c>
       <c r="M78" t="n">
-        <v>0.001600734690044368</v>
+        <v>0.03222513334691137</v>
       </c>
       <c r="N78" t="n">
-        <v>422.4298600619605</v>
+        <v>0.007392454194562144</v>
       </c>
       <c r="O78" t="n">
-        <v>3.858696616045661</v>
+        <v>73.92454194562146</v>
       </c>
       <c r="P78" t="n">
-        <v>422.4298600619605</v>
-      </c>
-      <c r="Q78" t="n">
-        <v>0.001704433894670024</v>
-      </c>
-      <c r="R78" t="n">
-        <v>0.9192245292837958</v>
-      </c>
-      <c r="S78" t="n">
-        <v>0.0310174920787642</v>
-      </c>
-      <c r="T78" t="n">
-        <v>0.0007125282255599638</v>
-      </c>
-      <c r="U78" t="n">
-        <v>1895</v>
-      </c>
-      <c r="V78" t="n">
-        <v>-0.001524967126455428</v>
-      </c>
-      <c r="W78" t="n">
-        <v>-15.24967126455428</v>
-      </c>
-      <c r="X78" t="n">
-        <v>15.24967126455428</v>
+        <v>73.92454194562146</v>
       </c>
     </row>
     <row r="79">
@@ -6443,46 +4555,22 @@
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>8.221813289249497e-05</v>
+        <v>0.002462340691338154</v>
       </c>
       <c r="L79" t="n">
-        <v>0.8221813289249498</v>
+        <v>24.62340691338154</v>
       </c>
       <c r="M79" t="n">
-        <v>0.0005094939218572446</v>
+        <v>0.0152466879797562</v>
       </c>
       <c r="N79" t="n">
-        <v>438.4090784586983</v>
+        <v>0.0006023406913381541</v>
       </c>
       <c r="O79" t="n">
-        <v>6.946664577148681</v>
+        <v>6.023406913381539</v>
       </c>
       <c r="P79" t="n">
-        <v>438.4090784586983</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>0.0005354727130028458</v>
-      </c>
-      <c r="R79" t="n">
-        <v>0.9192245292837958</v>
-      </c>
-      <c r="S79" t="n">
-        <v>0.01143574900723435</v>
-      </c>
-      <c r="T79" t="n">
-        <v>0.0002626999606345496</v>
-      </c>
-      <c r="U79" t="n">
-        <v>1895</v>
-      </c>
-      <c r="V79" t="n">
-        <v>-0.001777781867107505</v>
-      </c>
-      <c r="W79" t="n">
-        <v>-17.77781867107505</v>
-      </c>
-      <c r="X79" t="n">
-        <v>17.77781867107505</v>
+        <v>6.023406913381539</v>
       </c>
     </row>
     <row r="80">
@@ -6519,46 +4607,22 @@
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>0.001872520538350205</v>
+        <v>0.01794109978579766</v>
       </c>
       <c r="L80" t="n">
-        <v>18.72520538350205</v>
+        <v>179.4109978579766</v>
       </c>
       <c r="M80" t="n">
-        <v>0.001593093200451978</v>
+        <v>0.01526319488237043</v>
       </c>
       <c r="N80" t="n">
-        <v>469.8697755462664</v>
+        <v>0.01627109978579766</v>
       </c>
       <c r="O80" t="n">
-        <v>0.6743797613610999</v>
+        <v>162.7109978579766</v>
       </c>
       <c r="P80" t="n">
-        <v>469.8697755462664</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>0.001566533122750563</v>
-      </c>
-      <c r="R80" t="n">
-        <v>0.9263124473240245</v>
-      </c>
-      <c r="S80" t="n">
-        <v>0.01215178802656794</v>
-      </c>
-      <c r="T80" t="n">
-        <v>0.0002721307434781264</v>
-      </c>
-      <c r="U80" t="n">
-        <v>1994</v>
-      </c>
-      <c r="V80" t="n">
-        <v>0.0002025205383502056</v>
-      </c>
-      <c r="W80" t="n">
-        <v>2.025205383502055</v>
-      </c>
-      <c r="X80" t="n">
-        <v>2.025205383502055</v>
+        <v>162.7109978579766</v>
       </c>
     </row>
     <row r="81">
@@ -6595,46 +4659,22 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>0.001645959595835678</v>
+        <v>0.007761258328152719</v>
       </c>
       <c r="L81" t="n">
-        <v>16.45959595835678</v>
+        <v>77.61258328152719</v>
       </c>
       <c r="M81" t="n">
-        <v>0.006412125615112285</v>
+        <v>0.03026469165411009</v>
       </c>
       <c r="N81" t="n">
-        <v>458.376564109852</v>
+        <v>0.006191258328152719</v>
       </c>
       <c r="O81" t="n">
-        <v>3.087967961103021</v>
+        <v>61.91258328152719</v>
       </c>
       <c r="P81" t="n">
-        <v>458.376564109852</v>
-      </c>
-      <c r="Q81" t="n">
-        <v>0.006960125141016521</v>
-      </c>
-      <c r="R81" t="n">
-        <v>0.9215385383915671</v>
-      </c>
-      <c r="S81" t="n">
-        <v>0.0560025205640822</v>
-      </c>
-      <c r="T81" t="n">
-        <v>0.001348773248055297</v>
-      </c>
-      <c r="U81" t="n">
-        <v>1724</v>
-      </c>
-      <c r="V81" t="n">
-        <v>7.59595958356779e-05</v>
-      </c>
-      <c r="W81" t="n">
-        <v>0.7595959583567797</v>
-      </c>
-      <c r="X81" t="n">
-        <v>0.7595959583567797</v>
+        <v>61.91258328152719</v>
       </c>
     </row>
     <row r="82">
@@ -6671,46 +4711,22 @@
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>0.0002108825541560843</v>
+        <v>0.001839530423218044</v>
       </c>
       <c r="L82" t="n">
-        <v>2.108825541560843</v>
+        <v>18.39530423218044</v>
       </c>
       <c r="M82" t="n">
-        <v>0.001489298382088786</v>
+        <v>0.012961716866013</v>
       </c>
       <c r="N82" t="n">
-        <v>430.7298772127156</v>
+        <v>0.0002295304232180439</v>
       </c>
       <c r="O82" t="n">
-        <v>5.597975570462952</v>
+        <v>2.295304232180438</v>
       </c>
       <c r="P82" t="n">
-        <v>430.7298772127156</v>
-      </c>
-      <c r="Q82" t="n">
-        <v>0.001662544475518492</v>
-      </c>
-      <c r="R82" t="n">
-        <v>0.9214408316228403</v>
-      </c>
-      <c r="S82" t="n">
-        <v>0.01787543841764458</v>
-      </c>
-      <c r="T82" t="n">
-        <v>0.0004306396992437122</v>
-      </c>
-      <c r="U82" t="n">
-        <v>1723</v>
-      </c>
-      <c r="V82" t="n">
-        <v>-0.001399117445843916</v>
-      </c>
-      <c r="W82" t="n">
-        <v>-13.99117445843916</v>
-      </c>
-      <c r="X82" t="n">
-        <v>13.99117445843916</v>
+        <v>2.295304232180438</v>
       </c>
     </row>
     <row r="83">
@@ -6747,46 +4763,22 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>0.006766113485290689</v>
+        <v>0.07021514959524369</v>
       </c>
       <c r="L83" t="n">
-        <v>67.6611348529069</v>
+        <v>702.1514959524369</v>
       </c>
       <c r="M83" t="n">
-        <v>0.002601909306352965</v>
+        <v>0.02695918449389452</v>
       </c>
       <c r="N83" t="n">
-        <v>189.1690960963217</v>
+        <v>0.0648351495952437</v>
       </c>
       <c r="O83" t="n">
-        <v>0.9639240384466701</v>
+        <v>648.3514959524369</v>
       </c>
       <c r="P83" t="n">
-        <v>189.1690960963217</v>
-      </c>
-      <c r="Q83" t="n">
-        <v>0.002678295785971595</v>
-      </c>
-      <c r="R83" t="n">
-        <v>0.9746042773825451</v>
-      </c>
-      <c r="S83" t="n">
-        <v>0.003779199974070111</v>
-      </c>
-      <c r="T83" t="n">
-        <v>8.450548042586212e-05</v>
-      </c>
-      <c r="U83" t="n">
-        <v>2000</v>
-      </c>
-      <c r="V83" t="n">
-        <v>0.00138611348529069</v>
-      </c>
-      <c r="W83" t="n">
-        <v>13.8611348529069</v>
-      </c>
-      <c r="X83" t="n">
-        <v>13.8611348529069</v>
+        <v>648.3514959524369</v>
       </c>
     </row>
     <row r="84">
@@ -6823,46 +4815,22 @@
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>0.0002984855539985095</v>
+        <v>0.02729506357946093</v>
       </c>
       <c r="L84" t="n">
-        <v>2.984855539985095</v>
+        <v>272.9506357946093</v>
       </c>
       <c r="M84" t="n">
-        <v>0.0005422949116733278</v>
+        <v>0.04949837077505881</v>
       </c>
       <c r="N84" t="n">
-        <v>280.3319696972168</v>
+        <v>0.02385506357946093</v>
       </c>
       <c r="O84" t="n">
-        <v>4.554095635715999</v>
+        <v>238.5506357946093</v>
       </c>
       <c r="P84" t="n">
-        <v>280.3319696972168</v>
-      </c>
-      <c r="Q84" t="n">
-        <v>0.0005579403767758959</v>
-      </c>
-      <c r="R84" t="n">
-        <v>0.9746042773825451</v>
-      </c>
-      <c r="S84" t="n">
-        <v>0.005962830332769747</v>
-      </c>
-      <c r="T84" t="n">
-        <v>0.0001333329396237085</v>
-      </c>
-      <c r="U84" t="n">
-        <v>2000</v>
-      </c>
-      <c r="V84" t="n">
-        <v>-0.00314151444600149</v>
-      </c>
-      <c r="W84" t="n">
-        <v>-31.4151444600149</v>
-      </c>
-      <c r="X84" t="n">
-        <v>31.4151444600149</v>
+        <v>238.5506357946093</v>
       </c>
     </row>
     <row r="85">
@@ -6899,46 +4867,22 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>4.863990220121541e-05</v>
+        <v>0.008359829921077085</v>
       </c>
       <c r="L85" t="n">
-        <v>0.4863990220121541</v>
+        <v>83.59829921077085</v>
       </c>
       <c r="M85" t="n">
-        <v>0.0001623077160356485</v>
+        <v>0.0278263473723581</v>
       </c>
       <c r="N85" t="n">
-        <v>336.9658059707786</v>
+        <v>0.005569829921077085</v>
       </c>
       <c r="O85" t="n">
-        <v>8.364431090397421</v>
+        <v>55.69829921077085</v>
       </c>
       <c r="P85" t="n">
-        <v>336.9658059707786</v>
-      </c>
-      <c r="Q85" t="n">
-        <v>0.0001675876018872917</v>
-      </c>
-      <c r="R85" t="n">
-        <v>0.9746042773825451</v>
-      </c>
-      <c r="S85" t="n">
-        <v>0.002150072471618953</v>
-      </c>
-      <c r="T85" t="n">
-        <v>4.807708203090967e-05</v>
-      </c>
-      <c r="U85" t="n">
-        <v>2000</v>
-      </c>
-      <c r="V85" t="n">
-        <v>-0.002741360097798785</v>
-      </c>
-      <c r="W85" t="n">
-        <v>-27.41360097798784</v>
-      </c>
-      <c r="X85" t="n">
-        <v>27.41360097798784</v>
+        <v>55.69829921077085</v>
       </c>
     </row>
     <row r="86">
@@ -6975,46 +4919,22 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>0.0006472431556208812</v>
+        <v>0.02724221372237068</v>
       </c>
       <c r="L86" t="n">
-        <v>6.472431556208813</v>
+        <v>272.4221372237068</v>
       </c>
       <c r="M86" t="n">
-        <v>0.0004933678688819553</v>
+        <v>0.02069562687192025</v>
       </c>
       <c r="N86" t="n">
-        <v>342.9592648103804</v>
+        <v>0.02452221372237068</v>
       </c>
       <c r="O86" t="n">
-        <v>0.8544926423775409</v>
+        <v>245.2221372237068</v>
       </c>
       <c r="P86" t="n">
-        <v>342.9592648103804</v>
-      </c>
-      <c r="Q86" t="n">
-        <v>0.0004950562897621741</v>
-      </c>
-      <c r="R86" t="n">
-        <v>0.9301711125254857</v>
-      </c>
-      <c r="S86" t="n">
-        <v>0.00834416313997419</v>
-      </c>
-      <c r="T86" t="n">
-        <v>0.0001867680214622777</v>
-      </c>
-      <c r="U86" t="n">
-        <v>1996</v>
-      </c>
-      <c r="V86" t="n">
-        <v>-0.002072756844379119</v>
-      </c>
-      <c r="W86" t="n">
-        <v>-20.72756844379118</v>
-      </c>
-      <c r="X86" t="n">
-        <v>20.72756844379118</v>
+        <v>245.2221372237068</v>
       </c>
     </row>
     <row r="87">
@@ -7051,46 +4971,22 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>0.0006345689585359772</v>
+        <v>0.01025109023128445</v>
       </c>
       <c r="L87" t="n">
-        <v>6.345689585359772</v>
+        <v>102.5109023128445</v>
       </c>
       <c r="M87" t="n">
-        <v>0.002244216541346529</v>
+        <v>0.03612086191945445</v>
       </c>
       <c r="N87" t="n">
-        <v>386.2444461571736</v>
+        <v>0.008051090231284447</v>
       </c>
       <c r="O87" t="n">
-        <v>3.964522321092725</v>
+        <v>80.51090231284448</v>
       </c>
       <c r="P87" t="n">
-        <v>386.2444461571736</v>
-      </c>
-      <c r="Q87" t="n">
-        <v>0.002356784606454519</v>
-      </c>
-      <c r="R87" t="n">
-        <v>0.9282226194064171</v>
-      </c>
-      <c r="S87" t="n">
-        <v>0.03371446971679259</v>
-      </c>
-      <c r="T87" t="n">
-        <v>0.0007761226951214809</v>
-      </c>
-      <c r="U87" t="n">
-        <v>1887</v>
-      </c>
-      <c r="V87" t="n">
-        <v>-0.001565431041464023</v>
-      </c>
-      <c r="W87" t="n">
-        <v>-15.65431041464023</v>
-      </c>
-      <c r="X87" t="n">
-        <v>15.65431041464023</v>
+        <v>80.51090231284448</v>
       </c>
     </row>
     <row r="88">
@@ -7127,46 +5023,22 @@
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>4.091004383538089e-05</v>
+        <v>0.00299707423322286</v>
       </c>
       <c r="L88" t="n">
-        <v>0.4091004383538089</v>
+        <v>29.9707423322286</v>
       </c>
       <c r="M88" t="n">
-        <v>0.0002624489132267355</v>
+        <v>0.01919064619699613</v>
       </c>
       <c r="N88" t="n">
-        <v>403.195007888073</v>
+        <v>0.0009270742332228598</v>
       </c>
       <c r="O88" t="n">
-        <v>7.191504654985609</v>
+        <v>9.270742332228597</v>
       </c>
       <c r="P88" t="n">
-        <v>403.195007888073</v>
-      </c>
-      <c r="Q88" t="n">
-        <v>0.0002711653522939434</v>
-      </c>
-      <c r="R88" t="n">
-        <v>0.9281928271525547</v>
-      </c>
-      <c r="S88" t="n">
-        <v>0.005617151929002248</v>
-      </c>
-      <c r="T88" t="n">
-        <v>0.0001293437137436194</v>
-      </c>
-      <c r="U88" t="n">
-        <v>1886</v>
-      </c>
-      <c r="V88" t="n">
-        <v>-0.002029089956164619</v>
-      </c>
-      <c r="W88" t="n">
-        <v>-20.29089956164619</v>
-      </c>
-      <c r="X88" t="n">
-        <v>20.29089956164619</v>
+        <v>9.270742332228597</v>
       </c>
     </row>
     <row r="89">
@@ -7203,46 +5075,22 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>0.002002810760301532</v>
+        <v>0.01874418360139848</v>
       </c>
       <c r="L89" t="n">
-        <v>20.02810760301532</v>
+        <v>187.4418360139848</v>
       </c>
       <c r="M89" t="n">
-        <v>0.001769447535223372</v>
+        <v>0.01654106436599208</v>
       </c>
       <c r="N89" t="n">
-        <v>433.5964585206405</v>
+        <v>0.01684418360139849</v>
       </c>
       <c r="O89" t="n">
-        <v>0.7003057759662368</v>
+        <v>168.4418360139848</v>
       </c>
       <c r="P89" t="n">
-        <v>433.5964585206405</v>
-      </c>
-      <c r="Q89" t="n">
-        <v>0.00171753905377653</v>
-      </c>
-      <c r="R89" t="n">
-        <v>0.9389135740351826</v>
-      </c>
-      <c r="S89" t="n">
-        <v>0.01276496877759844</v>
-      </c>
-      <c r="T89" t="n">
-        <v>0.0002862215737634278</v>
-      </c>
-      <c r="U89" t="n">
-        <v>1989</v>
-      </c>
-      <c r="V89" t="n">
-        <v>0.0001028107603015316</v>
-      </c>
-      <c r="W89" t="n">
-        <v>1.028107603015318</v>
-      </c>
-      <c r="X89" t="n">
-        <v>1.028107603015318</v>
+        <v>168.4418360139848</v>
       </c>
     </row>
     <row r="90">
@@ -7279,46 +5127,22 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>0.001733599472355022</v>
+        <v>0.007790596398229537</v>
       </c>
       <c r="L90" t="n">
-        <v>17.33599472355022</v>
+        <v>77.90596398229538</v>
       </c>
       <c r="M90" t="n">
-        <v>0.007057573663818821</v>
+        <v>0.03172524977003544</v>
       </c>
       <c r="N90" t="n">
-        <v>424.019689706564</v>
+        <v>0.006000596398229537</v>
       </c>
       <c r="O90" t="n">
-        <v>3.226982333892883</v>
+        <v>60.00596398229538</v>
       </c>
       <c r="P90" t="n">
-        <v>424.019689706564</v>
-      </c>
-      <c r="Q90" t="n">
-        <v>0.007480991145327544</v>
-      </c>
-      <c r="R90" t="n">
-        <v>0.9340489490630692</v>
-      </c>
-      <c r="S90" t="n">
-        <v>0.05737302672080426</v>
-      </c>
-      <c r="T90" t="n">
-        <v>0.001383386516114956</v>
-      </c>
-      <c r="U90" t="n">
-        <v>1720</v>
-      </c>
-      <c r="V90" t="n">
-        <v>-5.640052764497813e-05</v>
-      </c>
-      <c r="W90" t="n">
-        <v>-0.5640052764497803</v>
-      </c>
-      <c r="X90" t="n">
-        <v>0.5640052764497803</v>
+        <v>60.00596398229538</v>
       </c>
     </row>
     <row r="91">
@@ -7355,46 +5179,22 @@
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>0.0002324034900306121</v>
+        <v>0.002229252326825732</v>
       </c>
       <c r="L91" t="n">
-        <v>2.32403490030612</v>
+        <v>22.29252326825732</v>
       </c>
       <c r="M91" t="n">
-        <v>0.001726321112511692</v>
+        <v>0.01653185214955006</v>
       </c>
       <c r="N91" t="n">
-        <v>399.5313871922842</v>
+        <v>0.0003492523268257318</v>
       </c>
       <c r="O91" t="n">
-        <v>5.888014494747859</v>
+        <v>3.492523268257319</v>
       </c>
       <c r="P91" t="n">
-        <v>399.5313871922842</v>
-      </c>
-      <c r="Q91" t="n">
-        <v>0.001846571132762265</v>
-      </c>
-      <c r="R91" t="n">
-        <v>0.9340489490630692</v>
-      </c>
-      <c r="S91" t="n">
-        <v>0.01879721637912393</v>
-      </c>
-      <c r="T91" t="n">
-        <v>0.000453241133780831</v>
-      </c>
-      <c r="U91" t="n">
-        <v>1720</v>
-      </c>
-      <c r="V91" t="n">
-        <v>-0.001647596509969388</v>
-      </c>
-      <c r="W91" t="n">
-        <v>-16.47596509969388</v>
-      </c>
-      <c r="X91" t="n">
-        <v>16.47596509969388</v>
+        <v>3.492523268257319</v>
       </c>
     </row>
     <row r="92">
@@ -7431,46 +5231,22 @@
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>0.007351249970026662</v>
+        <v>0.07463215151746008</v>
       </c>
       <c r="L92" t="n">
-        <v>73.51249970026662</v>
+        <v>746.3215151746008</v>
       </c>
       <c r="M92" t="n">
-        <v>0.002844270944697463</v>
+        <v>0.02883306955778284</v>
       </c>
       <c r="N92" t="n">
-        <v>159.3504012851974</v>
+        <v>0.06709215151746008</v>
       </c>
       <c r="O92" t="n">
-        <v>0.969839142970162</v>
+        <v>670.9215151746008</v>
       </c>
       <c r="P92" t="n">
-        <v>159.3504012851974</v>
-      </c>
-      <c r="Q92" t="n">
-        <v>0.002919221568371713</v>
-      </c>
-      <c r="R92" t="n">
-        <v>0.9775925559526909</v>
-      </c>
-      <c r="S92" t="n">
-        <v>0.004012646607961519</v>
-      </c>
-      <c r="T92" t="n">
-        <v>8.972550585085904e-05</v>
-      </c>
-      <c r="U92" t="n">
-        <v>2000</v>
-      </c>
-      <c r="V92" t="n">
-        <v>-0.0001887500299733386</v>
-      </c>
-      <c r="W92" t="n">
-        <v>-1.887500299733389</v>
-      </c>
-      <c r="X92" t="n">
-        <v>1.887500299733389</v>
+        <v>670.9215151746008</v>
       </c>
     </row>
     <row r="93">
@@ -7507,46 +5283,22 @@
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>0.0005577607619100524</v>
+        <v>0.02975455500239488</v>
       </c>
       <c r="L93" t="n">
-        <v>5.577607619100524</v>
+        <v>297.5455500239488</v>
       </c>
       <c r="M93" t="n">
-        <v>0.001026399573551006</v>
+        <v>0.05461418802512914</v>
       </c>
       <c r="N93" t="n">
-        <v>247.1619478625194</v>
+        <v>0.02551455500239488</v>
       </c>
       <c r="O93" t="n">
-        <v>4.612734290095251</v>
+        <v>255.1455500239488</v>
       </c>
       <c r="P93" t="n">
-        <v>247.1619478625194</v>
-      </c>
-      <c r="Q93" t="n">
-        <v>0.001052535397856911</v>
-      </c>
-      <c r="R93" t="n">
-        <v>0.9775925559526909</v>
-      </c>
-      <c r="S93" t="n">
-        <v>0.008099323365430615</v>
-      </c>
-      <c r="T93" t="n">
-        <v>0.0001811063761685523</v>
-      </c>
-      <c r="U93" t="n">
-        <v>2000</v>
-      </c>
-      <c r="V93" t="n">
-        <v>-0.003682239238089947</v>
-      </c>
-      <c r="W93" t="n">
-        <v>-36.82239238089947</v>
-      </c>
-      <c r="X93" t="n">
-        <v>36.82239238089947</v>
+        <v>255.1455500239488</v>
       </c>
     </row>
     <row r="94">
@@ -7583,46 +5335,22 @@
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>5.666792318647927e-05</v>
+        <v>0.009380282047031507</v>
       </c>
       <c r="L94" t="n">
-        <v>0.5666792318647927</v>
+        <v>93.80282047031507</v>
       </c>
       <c r="M94" t="n">
-        <v>0.0001927318845550817</v>
+        <v>0.03179094923332335</v>
       </c>
       <c r="N94" t="n">
-        <v>308.5484188303332</v>
+        <v>0.006020282047031507</v>
       </c>
       <c r="O94" t="n">
-        <v>8.525231984572763</v>
+        <v>60.20282047031507</v>
       </c>
       <c r="P94" t="n">
-        <v>308.5484188303332</v>
-      </c>
-      <c r="Q94" t="n">
-        <v>0.0001984583058269739</v>
-      </c>
-      <c r="R94" t="n">
-        <v>0.9775925559526909</v>
-      </c>
-      <c r="S94" t="n">
-        <v>0.002403870882586559</v>
-      </c>
-      <c r="T94" t="n">
-        <v>5.375218702595962e-05</v>
-      </c>
-      <c r="U94" t="n">
-        <v>2000</v>
-      </c>
-      <c r="V94" t="n">
-        <v>-0.003303332076813521</v>
-      </c>
-      <c r="W94" t="n">
-        <v>-33.03332076813521</v>
-      </c>
-      <c r="X94" t="n">
-        <v>33.03332076813521</v>
+        <v>60.20282047031507</v>
       </c>
     </row>
     <row r="95">
@@ -7659,46 +5387,22 @@
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>0.000610299251659058</v>
+        <v>0.02798726006320267</v>
       </c>
       <c r="L95" t="n">
-        <v>6.10299251659058</v>
+        <v>279.8726006320267</v>
       </c>
       <c r="M95" t="n">
-        <v>0.0004743488024315333</v>
+        <v>0.02164830824776462</v>
       </c>
       <c r="N95" t="n">
-        <v>312.5182802748704</v>
+        <v>0.02506726006320267</v>
       </c>
       <c r="O95" t="n">
-        <v>0.871284329420383</v>
+        <v>250.6726006320267</v>
       </c>
       <c r="P95" t="n">
-        <v>312.5182802748704</v>
-      </c>
-      <c r="Q95" t="n">
-        <v>0.0004692898284174916</v>
-      </c>
-      <c r="R95" t="n">
-        <v>0.9403623649086849</v>
-      </c>
-      <c r="S95" t="n">
-        <v>0.005437325796392592</v>
-      </c>
-      <c r="T95" t="n">
-        <v>0.0001215823009654702</v>
-      </c>
-      <c r="U95" t="n">
-        <v>2000</v>
-      </c>
-      <c r="V95" t="n">
-        <v>-0.002309700748340942</v>
-      </c>
-      <c r="W95" t="n">
-        <v>-23.09700748340942</v>
-      </c>
-      <c r="X95" t="n">
-        <v>23.09700748340942</v>
+        <v>250.6726006320267</v>
       </c>
     </row>
     <row r="96">
@@ -7735,46 +5439,22 @@
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>0.001291371550405273</v>
+        <v>0.01000820696053585</v>
       </c>
       <c r="L96" t="n">
-        <v>12.91371550405273</v>
+        <v>100.0820696053585</v>
       </c>
       <c r="M96" t="n">
-        <v>0.004678819418034571</v>
+        <v>0.0360756791334365</v>
       </c>
       <c r="N96" t="n">
-        <v>360.5287880126581</v>
+        <v>0.007648206960535851</v>
       </c>
       <c r="O96" t="n">
-        <v>4.061533140166466</v>
+        <v>76.4820696053585</v>
       </c>
       <c r="P96" t="n">
-        <v>360.5287880126581</v>
-      </c>
-      <c r="Q96" t="n">
-        <v>0.004840433502737196</v>
-      </c>
-      <c r="R96" t="n">
-        <v>0.9381115185308705</v>
-      </c>
-      <c r="S96" t="n">
-        <v>0.05203115136884597</v>
-      </c>
-      <c r="T96" t="n">
-        <v>0.001205148271639248</v>
-      </c>
-      <c r="U96" t="n">
-        <v>1864</v>
-      </c>
-      <c r="V96" t="n">
-        <v>-0.001068628449594727</v>
-      </c>
-      <c r="W96" t="n">
-        <v>-10.68628449594727</v>
-      </c>
-      <c r="X96" t="n">
-        <v>10.68628449594727</v>
+        <v>76.4820696053585</v>
       </c>
     </row>
     <row r="97">
@@ -7811,46 +5491,22 @@
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>0.0001914231169472663</v>
+        <v>0.003368129672930229</v>
       </c>
       <c r="L97" t="n">
-        <v>1.914231169472663</v>
+        <v>33.68129672930228</v>
       </c>
       <c r="M97" t="n">
-        <v>0.001263735217941123</v>
+        <v>0.02217582560023525</v>
       </c>
       <c r="N97" t="n">
-        <v>381.0665583987308</v>
+        <v>0.001148129672930229</v>
       </c>
       <c r="O97" t="n">
-        <v>7.400594984945332</v>
+        <v>11.48129672930228</v>
       </c>
       <c r="P97" t="n">
-        <v>381.0665583987308</v>
-      </c>
-      <c r="Q97" t="n">
-        <v>0.001290664734749832</v>
-      </c>
-      <c r="R97" t="n">
-        <v>0.9381115185308705</v>
-      </c>
-      <c r="S97" t="n">
-        <v>0.0187839170857804</v>
-      </c>
-      <c r="T97" t="n">
-        <v>0.0004350740780281385</v>
-      </c>
-      <c r="U97" t="n">
-        <v>1864</v>
-      </c>
-      <c r="V97" t="n">
-        <v>-0.002028576883052734</v>
-      </c>
-      <c r="W97" t="n">
-        <v>-20.28576883052733</v>
-      </c>
-      <c r="X97" t="n">
-        <v>20.28576883052733</v>
+        <v>11.48129672930228</v>
       </c>
     </row>
     <row r="98">
@@ -7887,46 +5543,22 @@
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>0.002116661619856877</v>
+        <v>0.01998504030991813</v>
       </c>
       <c r="L98" t="n">
-        <v>21.16661619856878</v>
+        <v>199.8504030991813</v>
       </c>
       <c r="M98" t="n">
-        <v>0.001928627611832882</v>
+        <v>0.01817120082323053</v>
       </c>
       <c r="N98" t="n">
-        <v>413.0807584105785</v>
+        <v>0.01797504030991813</v>
       </c>
       <c r="O98" t="n">
-        <v>0.7222488837314298</v>
+        <v>179.7504030991813</v>
       </c>
       <c r="P98" t="n">
-        <v>413.0807584105785</v>
-      </c>
-      <c r="Q98" t="n">
-        <v>0.001846691901050184</v>
-      </c>
-      <c r="R98" t="n">
-        <v>0.953134051989999</v>
-      </c>
-      <c r="S98" t="n">
-        <v>0.01351105444992472</v>
-      </c>
-      <c r="T98" t="n">
-        <v>0.0003023432044785474</v>
-      </c>
-      <c r="U98" t="n">
-        <v>1997</v>
-      </c>
-      <c r="V98" t="n">
-        <v>0.0001066616198568773</v>
-      </c>
-      <c r="W98" t="n">
-        <v>1.066616198568774</v>
-      </c>
-      <c r="X98" t="n">
-        <v>1.066616198568774</v>
+        <v>179.7504030991813</v>
       </c>
     </row>
     <row r="99">
@@ -7963,46 +5595,22 @@
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>0.001884039639604504</v>
+        <v>0.008411089723302852</v>
       </c>
       <c r="L99" t="n">
-        <v>18.84039639604504</v>
+        <v>84.11089723302852</v>
       </c>
       <c r="M99" t="n">
-        <v>0.007936418572412961</v>
+        <v>0.03544028972194662</v>
       </c>
       <c r="N99" t="n">
-        <v>406.0480768388868</v>
+        <v>0.006541089723302852</v>
       </c>
       <c r="O99" t="n">
-        <v>3.339061844778866</v>
+        <v>65.41089723302852</v>
       </c>
       <c r="P99" t="n">
-        <v>406.0480768388868</v>
-      </c>
-      <c r="Q99" t="n">
-        <v>0.008169306197237103</v>
-      </c>
-      <c r="R99" t="n">
-        <v>0.9483125714320702</v>
-      </c>
-      <c r="S99" t="n">
-        <v>0.06095549665093142</v>
-      </c>
-      <c r="T99" t="n">
-        <v>0.001471479555264962</v>
-      </c>
-      <c r="U99" t="n">
-        <v>1716</v>
-      </c>
-      <c r="V99" t="n">
-        <v>1.403963960450367e-05</v>
-      </c>
-      <c r="W99" t="n">
-        <v>0.1403963960450376</v>
-      </c>
-      <c r="X99" t="n">
-        <v>0.1403963960450376</v>
+        <v>65.41089723302852</v>
       </c>
     </row>
     <row r="100">
@@ -8039,46 +5647,22 @@
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>0.0002763906987364097</v>
+        <v>0.002474274866491189</v>
       </c>
       <c r="L100" t="n">
-        <v>2.763906987364097</v>
+        <v>24.74274866491189</v>
       </c>
       <c r="M100" t="n">
-        <v>0.002131037159854184</v>
+        <v>0.01907619449425696</v>
       </c>
       <c r="N100" t="n">
-        <v>384.0540885293677</v>
+        <v>0.0004942748664911894</v>
       </c>
       <c r="O100" t="n">
-        <v>6.111636742101593</v>
+        <v>4.942748664911893</v>
       </c>
       <c r="P100" t="n">
-        <v>384.0540885293677</v>
-      </c>
-      <c r="Q100" t="n">
-        <v>0.002163447566560224</v>
-      </c>
-      <c r="R100" t="n">
-        <v>0.9483125714320702</v>
-      </c>
-      <c r="S100" t="n">
-        <v>0.02237841017791117</v>
-      </c>
-      <c r="T100" t="n">
-        <v>0.0005402199123190384</v>
-      </c>
-      <c r="U100" t="n">
-        <v>1716</v>
-      </c>
-      <c r="V100" t="n">
-        <v>-0.00170360930126359</v>
-      </c>
-      <c r="W100" t="n">
-        <v>-17.0360930126359</v>
-      </c>
-      <c r="X100" t="n">
-        <v>17.0360930126359</v>
+        <v>4.942748664911893</v>
       </c>
     </row>
     <row r="101">
@@ -8115,46 +5699,22 @@
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>0.006758228532481356</v>
+        <v>0.07476706391046532</v>
       </c>
       <c r="L101" t="n">
-        <v>67.58228532481355</v>
+        <v>747.6706391046532</v>
       </c>
       <c r="M101" t="n">
-        <v>0.002619931039065785</v>
+        <v>0.0288978186752197</v>
       </c>
       <c r="N101" t="n">
-        <v>146.7244782438159</v>
+        <v>0.06782706391046532</v>
       </c>
       <c r="O101" t="n">
-        <v>0.9717329309807251</v>
+        <v>678.2706391046532</v>
       </c>
       <c r="P101" t="n">
-        <v>146.7244782438159</v>
-      </c>
-      <c r="Q101" t="n">
-        <v>0.002684086367330866</v>
-      </c>
-      <c r="R101" t="n">
-        <v>0.9796305411596243</v>
-      </c>
-      <c r="S101" t="n">
-        <v>0.003931490361163809</v>
-      </c>
-      <c r="T101" t="n">
-        <v>8.791079700447476e-05</v>
-      </c>
-      <c r="U101" t="n">
-        <v>2000</v>
-      </c>
-      <c r="V101" t="n">
-        <v>-0.0001817714675186452</v>
-      </c>
-      <c r="W101" t="n">
-        <v>-1.817714675186451</v>
-      </c>
-      <c r="X101" t="n">
-        <v>1.817714675186451</v>
+        <v>678.2706391046532</v>
       </c>
     </row>
   </sheetData>
